--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_32_45.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_32_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3886922.54271389</v>
+        <v>3859734.909075249</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36605210.56259097</v>
+        <v>36605210.56259096</v>
       </c>
     </row>
   </sheetData>
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1545416927480369</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>351.867973050014</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
         <v>2.651844648825261</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>107.4603054113278</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -717,13 +717,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809475</v>
+        <v>506</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>92.31538315628988</v>
       </c>
     </row>
     <row r="3">
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>238.490449687518</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>196.7608198536127</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>97.57360471312109</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>506</v>
+        <v>292.55979792854</v>
       </c>
       <c r="S3" t="n">
-        <v>55.57697166272453</v>
+        <v>455.5769716627245</v>
       </c>
       <c r="T3" t="n">
         <v>2.973567104306255</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -909,7 +909,7 @@
         <v>2.651844648825256</v>
       </c>
       <c r="H5" t="n">
-        <v>51.22504736769366</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>107.4603054113278</v>
@@ -939,16 +939,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>15.11934696336853</v>
+        <v>181.4334983257819</v>
       </c>
       <c r="S5" t="n">
-        <v>469.6559567470465</v>
+        <v>318.2804312395822</v>
       </c>
       <c r="T5" t="n">
-        <v>506</v>
+        <v>181.836134492383</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>249.1328543375554</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -960,7 +960,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1018,22 +1018,22 @@
         <v>97.57360471312109</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>250.0328781876495</v>
       </c>
       <c r="S6" t="n">
         <v>55.57697166272451</v>
       </c>
       <c r="T6" t="n">
-        <v>293.68103276161</v>
+        <v>402.9735671043063</v>
       </c>
       <c r="U6" t="n">
         <v>400.1714446658471</v>
       </c>
       <c r="V6" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1137,13 +1137,13 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>239.6063400916508</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>2.651844648825256</v>
+        <v>2.651844648825261</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>69.65595674704652</v>
+        <v>69.6559567470465</v>
       </c>
       <c r="T8" t="n">
-        <v>181.836134492383</v>
+        <v>319.3544127220286</v>
       </c>
       <c r="U8" t="n">
         <v>249.1328543375554</v>
@@ -1191,7 +1191,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>223.1743557825288</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -1222,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.1480264410651</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>274.5731973490766</v>
+        <v>326.4553513373645</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>97.57360471312109</v>
       </c>
       <c r="R9" t="n">
         <v>110.5483255942661</v>
       </c>
       <c r="S9" t="n">
-        <v>55.57697166272451</v>
+        <v>213.5594879465128</v>
       </c>
       <c r="T9" t="n">
-        <v>2.973567104306269</v>
+        <v>2.973567104306255</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1714446658471047</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1368,7 +1368,7 @@
         <v>264.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>232.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>187.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>149.7793472628416</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1419,19 +1419,19 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>364.836134492383</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>432.1328543375554</v>
       </c>
       <c r="V11" t="n">
-        <v>412.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>421.3734759809475</v>
+        <v>232.1172320710127</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>375.2818334606677</v>
       </c>
       <c r="Y11" t="n">
         <v>294.3174326828064</v>
@@ -1447,7 +1447,7 @@
         <v>167.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>24.2031821509449</v>
+        <v>31.99588503472753</v>
       </c>
       <c r="D12" t="n">
         <v>130.9376868977026</v>
@@ -1456,10 +1456,10 @@
         <v>125.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>122.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>108.1480264410651</v>
       </c>
       <c r="H12" t="n">
         <v>109.4553513373645</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>238.5769716627245</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>185.9735671043063</v>
@@ -1526,16 +1526,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35.21733379334555</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>45.42557417026224</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>63.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>57.38285596774193</v>
       </c>
       <c r="G13" t="n">
         <v>27.54797120218577</v>
@@ -1550,16 +1550,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>13.9060197027824</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>132.8205789774513</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>278.2985998618488</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>221.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>189.4745782429939</v>
       </c>
       <c r="D14" t="n">
         <v>150.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>144.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>144.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>136.6876737789043</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,16 +1653,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>209.6559567470465</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>321.836134492383</v>
+        <v>17.54420429225728</v>
       </c>
       <c r="U14" t="n">
-        <v>59.94601230865076</v>
+        <v>389.1328543375554</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>369.8510241668239</v>
       </c>
       <c r="W14" t="n">
         <v>378.3734759809475</v>
@@ -1766,13 +1766,13 @@
         <v>12.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>25.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>20.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>14.38285596774193</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1802,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>138.3991639961826</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>424.314266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>380.616832123963</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>93.73126658810133</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>27.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -1842,7 +1842,7 @@
         <v>202.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>170.4745782429939</v>
+        <v>16.01522470151595</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1851,13 +1851,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>123.6518446488253</v>
       </c>
       <c r="H17" t="n">
-        <v>81.1277911157097</v>
+        <v>117.6876737789043</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>190.6559567470465</v>
       </c>
       <c r="T17" t="n">
-        <v>302.836134492383</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>370.1328543375554</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>232.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -2030,25 +2030,25 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>40.76050327702752</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>291.3521214560641</v>
       </c>
       <c r="P19" t="n">
         <v>348.4708481479496</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>249.4442354066092</v>
       </c>
       <c r="R19" t="n">
-        <v>425.3045869975445</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>74.73126658810133</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>201.9993129555745</v>
       </c>
       <c r="C20" t="n">
         <v>169.4745782429939</v>
@@ -2085,13 +2085,13 @@
         <v>130.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>124.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>124.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>122.6518446488253</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2127,25 +2127,25 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>189.6559567470465</v>
       </c>
       <c r="T20" t="n">
-        <v>214.6089485681239</v>
+        <v>301.836134492383</v>
       </c>
       <c r="U20" t="n">
-        <v>369.1328543375554</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>349.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>358.3734759809475</v>
+        <v>76.92937151185414</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>312.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>231.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2240,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>5.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>69.82057897745131</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>162.8967753369761</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>177.2639467774783</v>
+        <v>347.4708481479496</v>
       </c>
       <c r="Q22" t="n">
-        <v>404.314266425598</v>
+        <v>129.2529698651288</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>424.3045869975445</v>
       </c>
       <c r="S22" t="n">
-        <v>73.73126658810133</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2319,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>130.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>124.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>349.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>358.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>217.5053905459833</v>
+        <v>312.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>231.3174326828064</v>
+        <v>32.86995913389297</v>
       </c>
     </row>
     <row r="24">
@@ -2507,19 +2507,19 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>215.2985998618488</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>290.3521214560641</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>347.4708481479496</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>404.314266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>395.3776836927101</v>
+        <v>149.2432904370753</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2556,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>159.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>159.0000000000047</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2583,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.478443882842787</v>
+        <v>3.478443882842674</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>38.4334983257819</v>
       </c>
       <c r="S26" t="n">
-        <v>159.0000000000011</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2610,16 +2610,16 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>101.6137016742076</v>
       </c>
       <c r="W26" t="n">
-        <v>159.0000000000002</v>
+        <v>159.0000000000029</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>159.0000000000029</v>
       </c>
       <c r="Y26" t="n">
-        <v>101.6137016742163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2632,10 +2632,10 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>159.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>159.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>159.0000000000046</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>159.0000000000049</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>53.76081985361269</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2683,19 +2683,19 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>159.0000000000013</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>140.0471999999982</v>
+        <v>159.0000000000034</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>86.28638014637433</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>139.9497502541235</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>10.94238389653595</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>64.90571404724132</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7.931342094130069</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>56.17031021621619</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>159.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.478443882842787</v>
+        <v>3.478443882842674</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>159.0000000000014</v>
+        <v>159.0000000000082</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>159.0000000000071</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>140.0471999999781</v>
       </c>
       <c r="X29" t="n">
-        <v>140.0471999999974</v>
+        <v>159.0000000000067</v>
       </c>
       <c r="Y29" t="n">
-        <v>159.0000000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>140.0471999999975</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>14.76081985361268</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,25 +2914,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>159.0000000000086</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>159.0000000000082</v>
       </c>
       <c r="T30" t="n">
-        <v>159.0000000000015</v>
+        <v>159.000000000008</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>125.2863801463625</v>
       </c>
       <c r="V30" t="n">
-        <v>159.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>159.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>70.44021621469844</v>
+        <v>105.1138003370787</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2999,22 +2999,22 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>25.90571404724133</v>
+        <v>25.90571404724132</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>17.17031021621619</v>
       </c>
       <c r="W31" t="n">
         <v>44.37280983870968</v>
       </c>
       <c r="X31" t="n">
-        <v>65.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>13.59975109151115</v>
       </c>
     </row>
     <row r="32">
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>140.0471999999799</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>159.000000000006</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>159.000000000006</v>
       </c>
       <c r="E32" t="n">
-        <v>159.0000000000008</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.478443882842787</v>
+        <v>3.478443882842674</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>159.0000000000018</v>
+        <v>159.000000000008</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>140.0471999999966</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>159.0000000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>140.0471999999965</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>159.0000000000008</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>14.76081985361268</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3157,19 +3157,19 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>159.0000000000018</v>
+        <v>159.0000000000081</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>159.0000000000075</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>159.000000000006</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>159.0000000000009</v>
+        <v>125.2863801463657</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>105.1138003370787</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>98.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>42.36210970817599</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.067680356721788</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>76.35144172041379</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3236,16 +3236,16 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>25.90571404724132</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>17.17031021621619</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>44.37280983870968</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>159.000000000001</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>159.0000000000018</v>
+        <v>140.0471999999807</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.478443882842787</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.478443882842674</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3318,13 +3318,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>140.0471999999963</v>
+        <v>159.0000000000071</v>
       </c>
       <c r="V35" t="n">
-        <v>159.0000000000009</v>
+        <v>159.000000000006</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>159.0000000000062</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3343,25 +3343,25 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>155.899173558932</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>159.000000000001</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>157.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>143.1480264410651</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>144.4553513373645</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>14.76081985361269</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>159.0000000000019</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>157.0467600300808</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>42.36210970817601</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3464,22 +3464,22 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.08636126729945</v>
       </c>
       <c r="R37" t="n">
-        <v>4.800275822581003</v>
+        <v>159</v>
       </c>
       <c r="S37" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>25.90571404724133</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>17.17031021621619</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>159.000000000001</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3510,10 +3510,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>140.0471999999827</v>
       </c>
       <c r="G38" t="n">
-        <v>140.0471999999972</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.478443882842787</v>
+        <v>3.478443882842562</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3555,19 +3555,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>159.0000000000069</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>159.0000000000053</v>
       </c>
       <c r="W38" t="n">
-        <v>159.0000000000008</v>
+        <v>159.0000000000051</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>159.0000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3577,28 +3577,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>155.8991735589332</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>159.0000000000009</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>157.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>143.1480264410651</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>14.76081985361269</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,22 +3631,22 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>159.0000000000064</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>126.6501378084985</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>159.0000000000055</v>
       </c>
       <c r="Y39" t="n">
-        <v>159.0000000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>90.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>42.36210970817599</v>
+        <v>42.36210970817601</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3698,10 +3698,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>76.35144172041379</v>
       </c>
       <c r="Q40" t="n">
-        <v>47.16931512729501</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3710,16 +3710,16 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>25.90571404724132</v>
+        <v>25.90571404724133</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>17.17031021621619</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>44.37280983870968</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3741,19 +3741,19 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>159.0000000000004</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>134.5868945886637</v>
+        <v>159.0000000000004</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>159.0000000000004</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>55.15339626288917</v>
       </c>
       <c r="I41" t="n">
         <v>5.460305411327823</v>
@@ -3768,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.478443882842787</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.478443882842674</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3783,22 +3783,22 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>79.4334983257819</v>
       </c>
       <c r="S41" t="n">
-        <v>159.0000000000031</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>159.0000000000034</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>159.0000000000019</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>140.0471999999999</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3823,16 +3823,16 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>159.0000000000022</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>140.0471999999931</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H42" t="n">
-        <v>159.0000000000028</v>
+        <v>159</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>159.0000000000019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>50.83430815999345</v>
+        <v>99.76565025412351</v>
       </c>
       <c r="U43" t="n">
-        <v>48.93134209413007</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>52.58689458867094</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>87.46030541132782</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.478443882842562</v>
+        <v>3.478443882842674</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4026,19 +4026,19 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>159.0000000000004</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>159.0000000000024</v>
+        <v>159.0000000000004</v>
       </c>
       <c r="W44" t="n">
-        <v>159.0000000000023</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>140.0471999999948</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4054,13 +4054,13 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>159.0000000000026</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>159.0000000000033</v>
+        <v>159</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>77.57360471312109</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>62.4735952868788</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>140.0471999999918</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>159.0000000000023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4190,10 +4190,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>19.39745025412353</v>
       </c>
       <c r="W46" t="n">
-        <v>19.39745025412353</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>861.9419335926402</v>
+        <v>221.4686892503811</v>
       </c>
       <c r="C2" t="n">
-        <v>811.9676121350706</v>
+        <v>171.4943677928115</v>
       </c>
       <c r="D2" t="n">
-        <v>456.5454171350564</v>
+        <v>161.0507761363976</v>
       </c>
       <c r="E2" t="n">
-        <v>452.1380538957951</v>
+        <v>156.6434128971363</v>
       </c>
       <c r="F2" t="n">
-        <v>43.15863095840936</v>
+        <v>151.7043940001546</v>
       </c>
       <c r="G2" t="n">
-        <v>40.48</v>
+        <v>149.0257630417453</v>
       </c>
       <c r="H2" t="n">
-        <v>40.48</v>
+        <v>149.0257630417453</v>
       </c>
       <c r="I2" t="n">
         <v>40.48</v>
@@ -4324,22 +4324,22 @@
         <v>98.67939743545104</v>
       </c>
       <c r="K2" t="n">
-        <v>599.619397435451</v>
+        <v>237.9003861289184</v>
       </c>
       <c r="L2" t="n">
-        <v>772.3353446716319</v>
+        <v>410.6163333650993</v>
       </c>
       <c r="M2" t="n">
+        <v>750.1568064492792</v>
+      </c>
+      <c r="N2" t="n">
         <v>1251.096806449279</v>
       </c>
-      <c r="N2" t="n">
-        <v>1752.036806449279</v>
-      </c>
       <c r="O2" t="n">
-        <v>1866.897695721682</v>
+        <v>1365.957695721682</v>
       </c>
       <c r="P2" t="n">
-        <v>2024</v>
+        <v>1523.06</v>
       </c>
       <c r="Q2" t="n">
         <v>2024</v>
@@ -4360,13 +4360,13 @@
         <v>1102.879325182232</v>
       </c>
       <c r="W2" t="n">
-        <v>862.0980363125877</v>
+        <v>591.7682140711206</v>
       </c>
       <c r="X2" t="n">
-        <v>862.0980363125877</v>
+        <v>397.5441398684259</v>
       </c>
       <c r="Y2" t="n">
-        <v>862.0980363125877</v>
+        <v>304.2962780943957</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>239.2283028824371</v>
+        <v>405.2273863086054</v>
       </c>
       <c r="C3" t="n">
-        <v>239.2283028824371</v>
+        <v>40.48</v>
       </c>
       <c r="D3" t="n">
-        <v>239.2283028824371</v>
+        <v>40.48</v>
       </c>
       <c r="E3" t="n">
-        <v>239.2283028824371</v>
+        <v>40.48</v>
       </c>
       <c r="F3" t="n">
-        <v>239.2283028824371</v>
+        <v>40.48</v>
       </c>
       <c r="G3" t="n">
-        <v>239.2283028824371</v>
+        <v>40.48</v>
       </c>
       <c r="H3" t="n">
-        <v>239.2283028824371</v>
+        <v>40.48</v>
       </c>
       <c r="I3" t="n">
         <v>40.48</v>
@@ -4421,31 +4421,31 @@
         <v>2024</v>
       </c>
       <c r="Q3" t="n">
-        <v>1925.44080332008</v>
+        <v>2024</v>
       </c>
       <c r="R3" t="n">
-        <v>1414.329692208969</v>
+        <v>1728.485052597434</v>
       </c>
       <c r="S3" t="n">
-        <v>1358.191336994096</v>
+        <v>1268.306293342157</v>
       </c>
       <c r="T3" t="n">
-        <v>1355.187733858433</v>
+        <v>1265.302690206494</v>
       </c>
       <c r="U3" t="n">
-        <v>1355.014557428284</v>
+        <v>1265.129513776346</v>
       </c>
       <c r="V3" t="n">
-        <v>1340.35731784089</v>
+        <v>1250.472274188952</v>
       </c>
       <c r="W3" t="n">
-        <v>903.6167694471239</v>
+        <v>813.7317257951854</v>
       </c>
       <c r="X3" t="n">
-        <v>883.5533962699648</v>
+        <v>793.6683526180262</v>
       </c>
       <c r="Y3" t="n">
-        <v>480.1277470112432</v>
+        <v>793.6683526180262</v>
       </c>
     </row>
     <row r="4">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>273.2111613389606</v>
+        <v>221.4686892503811</v>
       </c>
       <c r="C5" t="n">
-        <v>223.2368398813909</v>
+        <v>171.4943677928115</v>
       </c>
       <c r="D5" t="n">
-        <v>212.793248224977</v>
+        <v>161.0507761363976</v>
       </c>
       <c r="E5" t="n">
-        <v>208.3858849857158</v>
+        <v>156.6434128971363</v>
       </c>
       <c r="F5" t="n">
-        <v>203.4468660887341</v>
+        <v>151.7043940001546</v>
       </c>
       <c r="G5" t="n">
-        <v>200.7682351303247</v>
+        <v>149.0257630417453</v>
       </c>
       <c r="H5" t="n">
         <v>149.0257630417453</v>
@@ -4564,46 +4564,46 @@
         <v>237.9003861289184</v>
       </c>
       <c r="L5" t="n">
-        <v>738.8403861289183</v>
+        <v>410.6163333650993</v>
       </c>
       <c r="M5" t="n">
-        <v>1022.12</v>
+        <v>911.5563333650994</v>
       </c>
       <c r="N5" t="n">
-        <v>1022.12</v>
+        <v>1412.496333365099</v>
       </c>
       <c r="O5" t="n">
-        <v>1523.06</v>
+        <v>1527.357222637502</v>
       </c>
       <c r="P5" t="n">
-        <v>2024</v>
+        <v>1684.45952691582</v>
       </c>
       <c r="Q5" t="n">
         <v>2024</v>
       </c>
       <c r="R5" t="n">
-        <v>2008.727932360234</v>
+        <v>1840.733840074968</v>
       </c>
       <c r="S5" t="n">
-        <v>1534.327976050086</v>
+        <v>1519.238454984481</v>
       </c>
       <c r="T5" t="n">
-        <v>1023.216864938974</v>
+        <v>1335.565591860861</v>
       </c>
       <c r="U5" t="n">
-        <v>1023.216864938974</v>
+        <v>1083.916244045149</v>
       </c>
       <c r="V5" t="n">
-        <v>791.044113255314</v>
+        <v>851.7434923614883</v>
       </c>
       <c r="W5" t="n">
-        <v>550.2628243856699</v>
+        <v>610.9622034918443</v>
       </c>
       <c r="X5" t="n">
-        <v>356.0387501829752</v>
+        <v>416.7381292891497</v>
       </c>
       <c r="Y5" t="n">
-        <v>356.0387501829752</v>
+        <v>304.2962780943957</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>729.6803429896864</v>
+        <v>738.065640524864</v>
       </c>
       <c r="C6" t="n">
-        <v>729.6803429896864</v>
+        <v>738.065640524864</v>
       </c>
       <c r="D6" t="n">
-        <v>729.6803429896864</v>
+        <v>386.6134315372855</v>
       </c>
       <c r="E6" t="n">
-        <v>383.5469114524009</v>
+        <v>40.48</v>
       </c>
       <c r="F6" t="n">
         <v>40.48</v>
@@ -4640,7 +4640,7 @@
         <v>219.7623432885065</v>
       </c>
       <c r="K6" t="n">
-        <v>503.5158032508144</v>
+        <v>502.738257882279</v>
       </c>
       <c r="L6" t="n">
         <v>901.2371746661584</v>
@@ -4661,28 +4661,28 @@
         <v>1925.44080332008</v>
       </c>
       <c r="R6" t="n">
-        <v>1925.44080332008</v>
+        <v>1672.882340504272</v>
       </c>
       <c r="S6" t="n">
-        <v>1869.302448105207</v>
+        <v>1616.743985289399</v>
       </c>
       <c r="T6" t="n">
-        <v>1572.654940265197</v>
+        <v>1209.699978113332</v>
       </c>
       <c r="U6" t="n">
-        <v>1168.441359794644</v>
+        <v>805.4863976427794</v>
       </c>
       <c r="V6" t="n">
-        <v>749.7437161668456</v>
+        <v>790.8291580553853</v>
       </c>
       <c r="W6" t="n">
-        <v>749.7437161668456</v>
+        <v>758.1290137020231</v>
       </c>
       <c r="X6" t="n">
-        <v>729.6803429896864</v>
+        <v>738.065640524864</v>
       </c>
       <c r="Y6" t="n">
-        <v>729.6803429896864</v>
+        <v>738.065640524864</v>
       </c>
     </row>
     <row r="7">
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>754.0509175052408</v>
+        <v>112.9229262086358</v>
       </c>
       <c r="C8" t="n">
-        <v>704.0765960476712</v>
+        <v>62.94860475106622</v>
       </c>
       <c r="D8" t="n">
-        <v>693.6330043912573</v>
+        <v>52.50501309465229</v>
       </c>
       <c r="E8" t="n">
-        <v>285.185237111592</v>
+        <v>48.09764985539103</v>
       </c>
       <c r="F8" t="n">
-        <v>43.15863095840935</v>
+        <v>43.15863095840936</v>
       </c>
       <c r="G8" t="n">
         <v>40.48</v>
@@ -4795,22 +4795,22 @@
         <v>40.48</v>
       </c>
       <c r="J8" t="n">
-        <v>98.67939743545104</v>
+        <v>524.6810866557462</v>
       </c>
       <c r="K8" t="n">
-        <v>237.9003861289184</v>
+        <v>663.9020753492135</v>
       </c>
       <c r="L8" t="n">
-        <v>521.1799999999998</v>
+        <v>836.6180225853944</v>
       </c>
       <c r="M8" t="n">
-        <v>521.1799999999998</v>
+        <v>836.6180225853944</v>
       </c>
       <c r="N8" t="n">
-        <v>521.1799999999998</v>
+        <v>1251.096806449279</v>
       </c>
       <c r="O8" t="n">
-        <v>1022.12</v>
+        <v>1365.957695721682</v>
       </c>
       <c r="P8" t="n">
         <v>1523.06</v>
@@ -4825,22 +4825,22 @@
         <v>1953.640447730256</v>
       </c>
       <c r="T8" t="n">
-        <v>1769.967584606637</v>
+        <v>1631.06023285952</v>
       </c>
       <c r="U8" t="n">
-        <v>1518.318236790924</v>
+        <v>1379.410885043807</v>
       </c>
       <c r="V8" t="n">
-        <v>1286.145485107264</v>
+        <v>1147.238133360147</v>
       </c>
       <c r="W8" t="n">
-        <v>1060.716842902689</v>
+        <v>906.456844490503</v>
       </c>
       <c r="X8" t="n">
-        <v>866.4927686999947</v>
+        <v>712.2327702878084</v>
       </c>
       <c r="Y8" t="n">
-        <v>754.0509175052408</v>
+        <v>599.7909190930545</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1011.006400238041</v>
+        <v>734.9802664473575</v>
       </c>
       <c r="C9" t="n">
-        <v>646.2590139294362</v>
+        <v>370.2328801387521</v>
       </c>
       <c r="D9" t="n">
-        <v>646.2590139294362</v>
+        <v>370.2328801387521</v>
       </c>
       <c r="E9" t="n">
-        <v>646.2590139294362</v>
+        <v>370.2328801387521</v>
       </c>
       <c r="F9" t="n">
-        <v>646.2590139294362</v>
+        <v>370.2328801387521</v>
       </c>
       <c r="G9" t="n">
-        <v>317.8266639889663</v>
+        <v>370.2328801387521</v>
       </c>
       <c r="H9" t="n">
         <v>40.48</v>
@@ -4877,16 +4877,16 @@
         <v>219.7623432885065</v>
       </c>
       <c r="K9" t="n">
-        <v>503.5158032508144</v>
+        <v>502.738257882279</v>
       </c>
       <c r="L9" t="n">
-        <v>902.0147200346937</v>
+        <v>901.2371746661584</v>
       </c>
       <c r="M9" t="n">
-        <v>1136.471511777553</v>
+        <v>1135.693966409018</v>
       </c>
       <c r="N9" t="n">
-        <v>1422.05512421531</v>
+        <v>1421.277578846775</v>
       </c>
       <c r="O9" t="n">
         <v>1799.647820624833</v>
@@ -4895,31 +4895,31 @@
         <v>2024</v>
       </c>
       <c r="Q9" t="n">
-        <v>2024</v>
+        <v>1925.44080332008</v>
       </c>
       <c r="R9" t="n">
-        <v>1912.335024652256</v>
+        <v>1813.775827972336</v>
       </c>
       <c r="S9" t="n">
-        <v>1856.196669437383</v>
+        <v>1598.059173480909</v>
       </c>
       <c r="T9" t="n">
-        <v>1853.19306630172</v>
+        <v>1595.055570345246</v>
       </c>
       <c r="U9" t="n">
-        <v>1853.19306630172</v>
+        <v>1594.882393915098</v>
       </c>
       <c r="V9" t="n">
-        <v>1838.535826714326</v>
+        <v>1580.225154327704</v>
       </c>
       <c r="W9" t="n">
-        <v>1838.535826714326</v>
+        <v>1143.484605933937</v>
       </c>
       <c r="X9" t="n">
-        <v>1414.432049496763</v>
+        <v>1123.421232756778</v>
       </c>
       <c r="Y9" t="n">
-        <v>1011.006400238041</v>
+        <v>1123.421232756778</v>
       </c>
     </row>
     <row r="10">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>616.3825800139873</v>
+        <v>40.48</v>
       </c>
       <c r="C11" t="n">
-        <v>381.5597737079328</v>
+        <v>40.48</v>
       </c>
       <c r="D11" t="n">
-        <v>381.5597737079328</v>
+        <v>40.48</v>
       </c>
       <c r="E11" t="n">
-        <v>381.5597737079328</v>
+        <v>40.48</v>
       </c>
       <c r="F11" t="n">
-        <v>191.7722699624663</v>
+        <v>40.48</v>
       </c>
       <c r="G11" t="n">
         <v>40.48</v>
@@ -5029,31 +5029,31 @@
         <v>40.48</v>
       </c>
       <c r="I11" t="n">
-        <v>40.48</v>
+        <v>148.9242976427855</v>
       </c>
       <c r="J11" t="n">
-        <v>524.6810866557462</v>
+        <v>633.1253842985316</v>
       </c>
       <c r="K11" t="n">
-        <v>863.5508592130984</v>
+        <v>987.1763729919988</v>
       </c>
       <c r="L11" t="n">
-        <v>1036.266806449279</v>
+        <v>1159.89232022818</v>
       </c>
       <c r="M11" t="n">
-        <v>1537.206806449279</v>
+        <v>1660.83232022818</v>
       </c>
       <c r="N11" t="n">
-        <v>1537.206806449279</v>
+        <v>1716.825969791803</v>
       </c>
       <c r="O11" t="n">
-        <v>1866.897695721682</v>
+        <v>1831.686859064206</v>
       </c>
       <c r="P11" t="n">
-        <v>2024</v>
+        <v>1988.789163342524</v>
       </c>
       <c r="Q11" t="n">
-        <v>2024</v>
+        <v>1988.789163342524</v>
       </c>
       <c r="R11" t="n">
         <v>2024</v>
@@ -5062,22 +5062,22 @@
         <v>2024</v>
       </c>
       <c r="T11" t="n">
-        <v>2024</v>
+        <v>1655.478652027896</v>
       </c>
       <c r="U11" t="n">
-        <v>2024</v>
+        <v>1218.980819363698</v>
       </c>
       <c r="V11" t="n">
-        <v>1606.978763467855</v>
+        <v>1218.980819363698</v>
       </c>
       <c r="W11" t="n">
-        <v>1181.348989749726</v>
+        <v>984.5189687869179</v>
       </c>
       <c r="X11" t="n">
-        <v>1181.348989749726</v>
+        <v>605.4464097357384</v>
       </c>
       <c r="Y11" t="n">
-        <v>884.0586537064869</v>
+        <v>308.1560736924995</v>
       </c>
     </row>
     <row r="12">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>434.6904218261866</v>
+        <v>675.6772618895448</v>
       </c>
       <c r="C12" t="n">
-        <v>410.2427630878584</v>
+        <v>643.3581860968907</v>
       </c>
       <c r="D12" t="n">
-        <v>277.9824732921991</v>
+        <v>511.0978963012314</v>
       </c>
       <c r="E12" t="n">
-        <v>151.0409609468329</v>
+        <v>384.1563839558651</v>
       </c>
       <c r="F12" t="n">
-        <v>151.0409609468329</v>
+        <v>260.2813916953834</v>
       </c>
       <c r="G12" t="n">
         <v>151.0409609468329</v>
@@ -5108,28 +5108,28 @@
         <v>40.48</v>
       </c>
       <c r="I12" t="n">
-        <v>42.96648227131967</v>
+        <v>60.51678834492346</v>
       </c>
       <c r="J12" t="n">
-        <v>222.2488255598262</v>
+        <v>239.79913163343</v>
       </c>
       <c r="K12" t="n">
-        <v>720.832285522134</v>
+        <v>736.5252156021435</v>
       </c>
       <c r="L12" t="n">
-        <v>1199.707337403065</v>
+        <v>965.6456892908227</v>
       </c>
       <c r="M12" t="n">
-        <v>1199.707337403065</v>
+        <v>965.6456892908227</v>
       </c>
       <c r="N12" t="n">
-        <v>1199.707337403065</v>
+        <v>965.6456892908227</v>
       </c>
       <c r="O12" t="n">
-        <v>1700.647337403065</v>
+        <v>1466.585689290823</v>
       </c>
       <c r="P12" t="n">
-        <v>1922.870312056088</v>
+        <v>1905.76786866599</v>
       </c>
       <c r="Q12" t="n">
         <v>2024</v>
@@ -5138,25 +5138,25 @@
         <v>2024</v>
       </c>
       <c r="S12" t="n">
-        <v>1783.013159936642</v>
+        <v>2024</v>
       </c>
       <c r="T12" t="n">
-        <v>1595.161071952494</v>
+        <v>1836.147912015852</v>
       </c>
       <c r="U12" t="n">
-        <v>1410.139410673861</v>
+        <v>1651.126250737219</v>
       </c>
       <c r="V12" t="n">
-        <v>1210.633686237982</v>
+        <v>1451.62052630134</v>
       </c>
       <c r="W12" t="n">
-        <v>993.0850570361347</v>
+        <v>1234.071897099493</v>
       </c>
       <c r="X12" t="n">
-        <v>788.1731990104906</v>
+        <v>1029.160039073849</v>
       </c>
       <c r="Y12" t="n">
-        <v>603.9394689436882</v>
+        <v>844.9263090070464</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>123.075222620423</v>
+        <v>244.216783722548</v>
       </c>
       <c r="C13" t="n">
-        <v>87.50215818270019</v>
+        <v>244.216783722548</v>
       </c>
       <c r="D13" t="n">
-        <v>87.50215818270019</v>
+        <v>198.3323653687477</v>
       </c>
       <c r="E13" t="n">
-        <v>87.50215818270019</v>
+        <v>133.7051887657613</v>
       </c>
       <c r="F13" t="n">
-        <v>87.50215818270019</v>
+        <v>75.74270799026442</v>
       </c>
       <c r="G13" t="n">
-        <v>59.67592464513879</v>
+        <v>47.91647445270303</v>
       </c>
       <c r="H13" t="n">
-        <v>52.23945019243577</v>
+        <v>40.48</v>
       </c>
       <c r="I13" t="n">
-        <v>106.9663127350761</v>
+        <v>95.20686254264029</v>
       </c>
       <c r="J13" t="n">
-        <v>321.5896968301503</v>
+        <v>309.8302466377146</v>
       </c>
       <c r="K13" t="n">
-        <v>321.5896968301503</v>
+        <v>295.7837620894496</v>
       </c>
       <c r="L13" t="n">
-        <v>321.5896968301503</v>
+        <v>161.621561102125</v>
       </c>
       <c r="M13" t="n">
-        <v>321.5896968301503</v>
+        <v>161.621561102125</v>
       </c>
       <c r="N13" t="n">
-        <v>40.48</v>
+        <v>161.621561102125</v>
       </c>
       <c r="O13" t="n">
-        <v>40.48</v>
+        <v>161.621561102125</v>
       </c>
       <c r="P13" t="n">
-        <v>40.48</v>
+        <v>161.621561102125</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.48</v>
+        <v>161.621561102125</v>
       </c>
       <c r="R13" t="n">
-        <v>40.48</v>
+        <v>161.621561102125</v>
       </c>
       <c r="S13" t="n">
-        <v>40.48</v>
+        <v>161.621561102125</v>
       </c>
       <c r="T13" t="n">
-        <v>49.4833430932311</v>
+        <v>170.6249041953561</v>
       </c>
       <c r="U13" t="n">
-        <v>114.8913144200423</v>
+        <v>236.0328755221673</v>
       </c>
       <c r="V13" t="n">
-        <v>132.5427073059883</v>
+        <v>253.6842684081133</v>
       </c>
       <c r="W13" t="n">
-        <v>123.075222620423</v>
+        <v>244.216783722548</v>
       </c>
       <c r="X13" t="n">
-        <v>123.075222620423</v>
+        <v>244.216783722548</v>
       </c>
       <c r="Y13" t="n">
-        <v>123.075222620423</v>
+        <v>244.216783722548</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>484.5123980350811</v>
+        <v>521.794553294695</v>
       </c>
       <c r="C14" t="n">
-        <v>484.5123980350811</v>
+        <v>330.4060904229839</v>
       </c>
       <c r="D14" t="n">
-        <v>332.6546649645258</v>
+        <v>178.5483573524286</v>
       </c>
       <c r="E14" t="n">
-        <v>186.8331603111231</v>
+        <v>178.5483573524286</v>
       </c>
       <c r="F14" t="n">
-        <v>40.48</v>
+        <v>178.5483573524286</v>
       </c>
       <c r="G14" t="n">
-        <v>40.48</v>
+        <v>178.5483573524286</v>
       </c>
       <c r="H14" t="n">
         <v>40.48</v>
@@ -5269,52 +5269,52 @@
         <v>40.48</v>
       </c>
       <c r="J14" t="n">
-        <v>98.67939743545104</v>
+        <v>524.6810866557462</v>
       </c>
       <c r="K14" t="n">
-        <v>364.0776957216816</v>
+        <v>921.3020753492135</v>
       </c>
       <c r="L14" t="n">
-        <v>865.0176957216815</v>
+        <v>1104.810475084827</v>
       </c>
       <c r="M14" t="n">
-        <v>865.0176957216815</v>
+        <v>1605.750475084827</v>
       </c>
       <c r="N14" t="n">
-        <v>865.0176957216815</v>
+        <v>1605.750475084827</v>
       </c>
       <c r="O14" t="n">
-        <v>1365.957695721682</v>
+        <v>1720.61136435723</v>
       </c>
       <c r="P14" t="n">
-        <v>1523.06</v>
+        <v>1877.713668635548</v>
       </c>
       <c r="Q14" t="n">
-        <v>2024</v>
+        <v>1946.219163342524</v>
       </c>
       <c r="R14" t="n">
         <v>2024</v>
       </c>
       <c r="S14" t="n">
-        <v>1812.226306316115</v>
+        <v>2024</v>
       </c>
       <c r="T14" t="n">
-        <v>1487.139301778354</v>
+        <v>2006.278581522972</v>
       </c>
       <c r="U14" t="n">
-        <v>1426.587774193858</v>
+        <v>1613.215092293118</v>
       </c>
       <c r="V14" t="n">
-        <v>1426.587774193858</v>
+        <v>1239.628199195316</v>
       </c>
       <c r="W14" t="n">
-        <v>1044.392343910073</v>
+        <v>857.4327689115311</v>
       </c>
       <c r="X14" t="n">
-        <v>708.7541282932372</v>
+        <v>521.794553294695</v>
       </c>
       <c r="Y14" t="n">
-        <v>708.7541282932372</v>
+        <v>521.794553294695</v>
       </c>
     </row>
     <row r="15">
@@ -5345,22 +5345,22 @@
         <v>40.48</v>
       </c>
       <c r="I15" t="n">
-        <v>85.53648227131967</v>
+        <v>40.48</v>
       </c>
       <c r="J15" t="n">
-        <v>422.4681162330131</v>
+        <v>219.7623432885065</v>
       </c>
       <c r="K15" t="n">
-        <v>923.4081162330131</v>
+        <v>503.5158032508144</v>
       </c>
       <c r="L15" t="n">
-        <v>1321.907033016892</v>
+        <v>902.0147200346937</v>
       </c>
       <c r="M15" t="n">
-        <v>1420.499118915242</v>
+        <v>1136.471511777553</v>
       </c>
       <c r="N15" t="n">
-        <v>1420.499118915242</v>
+        <v>1422.05512421531</v>
       </c>
       <c r="O15" t="n">
         <v>1798.8693606933</v>
@@ -5403,55 +5403,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>278.5867394816989</v>
+        <v>250.8439588256764</v>
       </c>
       <c r="C16" t="n">
-        <v>265.7329549887245</v>
+        <v>237.9901743327019</v>
       </c>
       <c r="D16" t="n">
-        <v>265.7329549887245</v>
+        <v>212.1960146806257</v>
       </c>
       <c r="E16" t="n">
-        <v>265.7329549887245</v>
+        <v>191.0031815119827</v>
       </c>
       <c r="F16" t="n">
-        <v>265.7329549887245</v>
+        <v>176.4750441708292</v>
       </c>
       <c r="G16" t="n">
-        <v>281.0304634985606</v>
+        <v>191.7725526806653</v>
       </c>
       <c r="H16" t="n">
-        <v>316.3119748874664</v>
+        <v>227.0540640695711</v>
       </c>
       <c r="I16" t="n">
-        <v>413.6088374301066</v>
+        <v>324.3509266122114</v>
       </c>
       <c r="J16" t="n">
-        <v>670.8022215251808</v>
+        <v>581.5443107072856</v>
       </c>
       <c r="K16" t="n">
-        <v>699.6052620194263</v>
+        <v>610.3473512015311</v>
       </c>
       <c r="L16" t="n">
-        <v>608.8774044664451</v>
+        <v>519.6194936485499</v>
       </c>
       <c r="M16" t="n">
-        <v>608.8774044664451</v>
+        <v>519.6194936485499</v>
       </c>
       <c r="N16" t="n">
-        <v>608.8774044664451</v>
+        <v>519.6194936485499</v>
       </c>
       <c r="O16" t="n">
-        <v>608.8774044664451</v>
+        <v>519.6194936485499</v>
       </c>
       <c r="P16" t="n">
-        <v>469.0802691167657</v>
+        <v>519.6194936485499</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.48</v>
+        <v>519.6194936485499</v>
       </c>
       <c r="R16" t="n">
-        <v>40.48</v>
+        <v>135.1580470586882</v>
       </c>
       <c r="S16" t="n">
         <v>40.48</v>
@@ -5472,7 +5472,7 @@
         <v>305.9744165898592</v>
       </c>
       <c r="Y16" t="n">
-        <v>305.9744165898592</v>
+        <v>278.2316359338366</v>
       </c>
     </row>
     <row r="17">
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>421.7850485522379</v>
+        <v>300.4342859891369</v>
       </c>
       <c r="C17" t="n">
-        <v>249.588504872446</v>
+        <v>284.257291341141</v>
       </c>
       <c r="D17" t="n">
-        <v>249.588504872446</v>
+        <v>284.257291341141</v>
       </c>
       <c r="E17" t="n">
-        <v>249.588504872446</v>
+        <v>284.257291341141</v>
       </c>
       <c r="F17" t="n">
-        <v>122.4272637532421</v>
+        <v>284.257291341141</v>
       </c>
       <c r="G17" t="n">
-        <v>122.4272637532421</v>
+        <v>159.3564381605094</v>
       </c>
       <c r="H17" t="n">
         <v>40.48</v>
@@ -5506,52 +5506,52 @@
         <v>40.48</v>
       </c>
       <c r="J17" t="n">
-        <v>524.6810866557462</v>
+        <v>98.67939743545104</v>
       </c>
       <c r="K17" t="n">
-        <v>1025.621086655746</v>
+        <v>237.9003861289184</v>
       </c>
       <c r="L17" t="n">
-        <v>1526.561086655746</v>
+        <v>410.6163333650993</v>
       </c>
       <c r="M17" t="n">
-        <v>1526.561086655746</v>
+        <v>911.5563333650994</v>
       </c>
       <c r="N17" t="n">
-        <v>1526.561086655746</v>
+        <v>1412.496333365099</v>
       </c>
       <c r="O17" t="n">
-        <v>1641.421975928149</v>
+        <v>1527.357222637502</v>
       </c>
       <c r="P17" t="n">
-        <v>1989.929599833498</v>
+        <v>1684.45952691582</v>
       </c>
       <c r="Q17" t="n">
-        <v>1989.929599833498</v>
+        <v>2024</v>
       </c>
       <c r="R17" t="n">
         <v>2024</v>
       </c>
       <c r="S17" t="n">
-        <v>2024</v>
+        <v>1831.418225508034</v>
       </c>
       <c r="T17" t="n">
-        <v>1718.104914654159</v>
+        <v>1831.418225508034</v>
       </c>
       <c r="U17" t="n">
-        <v>1344.233344616224</v>
+        <v>1457.546655470099</v>
       </c>
       <c r="V17" t="n">
-        <v>989.838370710341</v>
+        <v>1103.151681564216</v>
       </c>
       <c r="W17" t="n">
-        <v>626.8348596184748</v>
+        <v>740.14817047235</v>
       </c>
       <c r="X17" t="n">
-        <v>626.8348596184748</v>
+        <v>740.14817047235</v>
       </c>
       <c r="Y17" t="n">
-        <v>626.8348596184748</v>
+        <v>505.4840970553738</v>
       </c>
     </row>
     <row r="18">
@@ -5591,13 +5591,13 @@
         <v>503.5158032508144</v>
       </c>
       <c r="L18" t="n">
-        <v>612.5799268558371</v>
+        <v>902.0147200346937</v>
       </c>
       <c r="M18" t="n">
-        <v>847.0367185986963</v>
+        <v>1136.471511777553</v>
       </c>
       <c r="N18" t="n">
-        <v>1132.620331036453</v>
+        <v>1422.05512421531</v>
       </c>
       <c r="O18" t="n">
         <v>1510.990572814512</v>
@@ -5673,22 +5673,22 @@
         <v>938.7297020309323</v>
       </c>
       <c r="M19" t="n">
-        <v>897.5574764985813</v>
+        <v>938.7297020309323</v>
       </c>
       <c r="N19" t="n">
-        <v>897.5574764985813</v>
+        <v>938.7297020309323</v>
       </c>
       <c r="O19" t="n">
-        <v>897.5574764985813</v>
+        <v>644.4346298530897</v>
       </c>
       <c r="P19" t="n">
-        <v>545.5667207935817</v>
+        <v>292.4438741480901</v>
       </c>
       <c r="Q19" t="n">
-        <v>545.5667207935817</v>
+        <v>40.48</v>
       </c>
       <c r="R19" t="n">
-        <v>115.966127866769</v>
+        <v>40.48</v>
       </c>
       <c r="S19" t="n">
         <v>40.48</v>
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>718.9835322692419</v>
+        <v>343.322155538226</v>
       </c>
       <c r="C20" t="n">
-        <v>547.7970895995511</v>
+        <v>172.1357128685352</v>
       </c>
       <c r="D20" t="n">
-        <v>416.141376731016</v>
+        <v>40.48</v>
       </c>
       <c r="E20" t="n">
-        <v>290.5218922796334</v>
+        <v>40.48</v>
       </c>
       <c r="F20" t="n">
-        <v>164.3707521705306</v>
+        <v>40.48</v>
       </c>
       <c r="G20" t="n">
         <v>40.48</v>
@@ -5740,25 +5740,25 @@
         <v>40.48</v>
       </c>
       <c r="I20" t="n">
-        <v>58.13445864069034</v>
+        <v>40.48</v>
       </c>
       <c r="J20" t="n">
-        <v>116.3338560761414</v>
+        <v>524.6810866557462</v>
       </c>
       <c r="K20" t="n">
-        <v>255.5548447696087</v>
+        <v>663.9020753492135</v>
       </c>
       <c r="L20" t="n">
-        <v>428.2707920057896</v>
+        <v>836.6180225853944</v>
       </c>
       <c r="M20" t="n">
-        <v>428.2707920057896</v>
+        <v>1251.096806449279</v>
       </c>
       <c r="N20" t="n">
-        <v>929.2107920057896</v>
+        <v>1251.096806449279</v>
       </c>
       <c r="O20" t="n">
-        <v>1044.071681278192</v>
+        <v>1365.957695721682</v>
       </c>
       <c r="P20" t="n">
         <v>1523.06</v>
@@ -5770,25 +5770,25 @@
         <v>2024</v>
       </c>
       <c r="S20" t="n">
-        <v>2024</v>
+        <v>1832.428326518135</v>
       </c>
       <c r="T20" t="n">
-        <v>1807.223284274622</v>
+        <v>1527.543342182394</v>
       </c>
       <c r="U20" t="n">
-        <v>1434.361815246789</v>
+        <v>1527.543342182394</v>
       </c>
       <c r="V20" t="n">
-        <v>1080.976942351007</v>
+        <v>1174.158469286613</v>
       </c>
       <c r="W20" t="n">
-        <v>718.9835322692419</v>
+        <v>1096.452033416053</v>
       </c>
       <c r="X20" t="n">
-        <v>718.9835322692419</v>
+        <v>781.0158380012369</v>
       </c>
       <c r="Y20" t="n">
-        <v>718.9835322692419</v>
+        <v>547.3618655943618</v>
       </c>
     </row>
     <row r="21">
@@ -5834,7 +5834,7 @@
         <v>1136.471511777553</v>
       </c>
       <c r="N21" t="n">
-        <v>1422.05512421531</v>
+        <v>1334.428020607082</v>
       </c>
       <c r="O21" t="n">
         <v>1712.798262385141</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>397.4336561358569</v>
+        <v>404.9744165898593</v>
       </c>
       <c r="C22" t="n">
-        <v>404.6356619542927</v>
+        <v>412.1764224082951</v>
       </c>
       <c r="D22" t="n">
-        <v>399.0435225042366</v>
+        <v>412.1764224082951</v>
       </c>
       <c r="E22" t="n">
-        <v>399.0435225042366</v>
+        <v>412.1764224082951</v>
       </c>
       <c r="F22" t="n">
-        <v>404.6044950961721</v>
+        <v>417.7373950002305</v>
       </c>
       <c r="G22" t="n">
-        <v>439.7020036060082</v>
+        <v>452.8349035100666</v>
       </c>
       <c r="H22" t="n">
-        <v>494.783514994914</v>
+        <v>507.9164148989724</v>
       </c>
       <c r="I22" t="n">
-        <v>611.8803775375543</v>
+        <v>625.0132774416127</v>
       </c>
       <c r="J22" t="n">
-        <v>888.8737616326285</v>
+        <v>902.0066615366869</v>
       </c>
       <c r="K22" t="n">
-        <v>937.476802126874</v>
+        <v>950.6097020309323</v>
       </c>
       <c r="L22" t="n">
-        <v>866.950964775913</v>
+        <v>950.6097020309323</v>
       </c>
       <c r="M22" t="n">
-        <v>702.408767465836</v>
+        <v>950.6097020309323</v>
       </c>
       <c r="N22" t="n">
-        <v>702.408767465836</v>
+        <v>950.6097020309323</v>
       </c>
       <c r="O22" t="n">
-        <v>702.408767465836</v>
+        <v>950.6097020309323</v>
       </c>
       <c r="P22" t="n">
-        <v>523.3542757714135</v>
+        <v>599.6290473360338</v>
       </c>
       <c r="Q22" t="n">
-        <v>114.956026856668</v>
+        <v>469.0704919167117</v>
       </c>
       <c r="R22" t="n">
-        <v>114.956026856668</v>
+        <v>40.48</v>
       </c>
       <c r="S22" t="n">
         <v>40.48</v>
@@ -5946,7 +5946,7 @@
         <v>404.9744165898593</v>
       </c>
       <c r="Y22" t="n">
-        <v>397.4336561358569</v>
+        <v>404.9744165898593</v>
       </c>
     </row>
     <row r="23">
@@ -5956,13 +5956,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>539.5122866408566</v>
+        <v>282.2370893209389</v>
       </c>
       <c r="C23" t="n">
-        <v>539.5122866408566</v>
+        <v>282.2370893209389</v>
       </c>
       <c r="D23" t="n">
-        <v>407.8565737723214</v>
+        <v>282.2370893209389</v>
       </c>
       <c r="E23" t="n">
         <v>282.2370893209389</v>
@@ -5977,22 +5977,22 @@
         <v>40.48</v>
       </c>
       <c r="I23" t="n">
-        <v>58.13445864069067</v>
+        <v>40.48</v>
       </c>
       <c r="J23" t="n">
-        <v>116.3338560761417</v>
+        <v>524.6810866557462</v>
       </c>
       <c r="K23" t="n">
-        <v>255.554844769609</v>
+        <v>1025.621086655746</v>
       </c>
       <c r="L23" t="n">
-        <v>428.2707920057899</v>
+        <v>1198.337033891927</v>
       </c>
       <c r="M23" t="n">
-        <v>428.27079200579</v>
+        <v>1251.096806449279</v>
       </c>
       <c r="N23" t="n">
-        <v>865.0176957216815</v>
+        <v>1251.096806449279</v>
       </c>
       <c r="O23" t="n">
         <v>1365.957695721682</v>
@@ -6019,13 +6019,13 @@
         <v>992.8686737406442</v>
       </c>
       <c r="W23" t="n">
-        <v>992.8686737406442</v>
+        <v>630.875263658879</v>
       </c>
       <c r="X23" t="n">
-        <v>773.1662590477317</v>
+        <v>315.4390682440632</v>
       </c>
       <c r="Y23" t="n">
-        <v>539.5122866408566</v>
+        <v>282.2370893209389</v>
       </c>
     </row>
     <row r="24">
@@ -6065,16 +6065,16 @@
         <v>503.5158032508144</v>
       </c>
       <c r="L24" t="n">
-        <v>883.0120241420791</v>
+        <v>902.0147200346937</v>
       </c>
       <c r="M24" t="n">
-        <v>1117.468815884938</v>
+        <v>1136.471511777553</v>
       </c>
       <c r="N24" t="n">
-        <v>1117.468815884938</v>
+        <v>1422.05512421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1495.839057662997</v>
+        <v>1712.798262385141</v>
       </c>
       <c r="P24" t="n">
         <v>1720.191237038164</v>
@@ -6150,16 +6150,16 @@
         <v>950.6097020309323</v>
       </c>
       <c r="N25" t="n">
-        <v>733.1363688371457</v>
+        <v>950.6097020309323</v>
       </c>
       <c r="O25" t="n">
-        <v>439.8513976694042</v>
+        <v>950.6097020309323</v>
       </c>
       <c r="P25" t="n">
-        <v>439.8513976694042</v>
+        <v>599.6290473360338</v>
       </c>
       <c r="Q25" t="n">
-        <v>439.8513976694042</v>
+        <v>191.2307984212882</v>
       </c>
       <c r="R25" t="n">
         <v>40.48</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>173.326060606061</v>
+        <v>173.3260606060653</v>
       </c>
       <c r="C26" t="n">
-        <v>173.326060606061</v>
+        <v>173.3260606060653</v>
       </c>
       <c r="D26" t="n">
-        <v>12.72</v>
+        <v>173.3260606060653</v>
       </c>
       <c r="E26" t="n">
-        <v>12.72</v>
+        <v>173.3260606060653</v>
       </c>
       <c r="F26" t="n">
-        <v>12.72</v>
+        <v>173.3260606060653</v>
       </c>
       <c r="G26" t="n">
-        <v>12.72</v>
+        <v>173.3260606060653</v>
       </c>
       <c r="H26" t="n">
         <v>12.72</v>
@@ -6226,13 +6226,13 @@
         <v>367.5503861289183</v>
       </c>
       <c r="M26" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="N26" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="O26" t="n">
-        <v>478.8976957216814</v>
+        <v>478.8976957216815</v>
       </c>
       <c r="P26" t="n">
         <v>636</v>
@@ -6244,25 +6244,25 @@
         <v>597.1782845194123</v>
       </c>
       <c r="S26" t="n">
-        <v>436.5722239133505</v>
+        <v>597.1782845194123</v>
       </c>
       <c r="T26" t="n">
-        <v>436.5722239133505</v>
+        <v>597.1782845194123</v>
       </c>
       <c r="U26" t="n">
-        <v>436.5722239133505</v>
+        <v>597.1782845194123</v>
       </c>
       <c r="V26" t="n">
-        <v>436.5722239133505</v>
+        <v>494.5381818181925</v>
       </c>
       <c r="W26" t="n">
-        <v>275.9661633072897</v>
+        <v>333.9321212121289</v>
       </c>
       <c r="X26" t="n">
-        <v>275.9661633072897</v>
+        <v>173.3260606060653</v>
       </c>
       <c r="Y26" t="n">
-        <v>173.326060606061</v>
+        <v>173.3260606060653</v>
       </c>
     </row>
     <row r="27">
@@ -6272,46 +6272,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>333.9321212121217</v>
+        <v>388.2359796501235</v>
       </c>
       <c r="C27" t="n">
-        <v>173.326060606061</v>
+        <v>388.2359796501235</v>
       </c>
       <c r="D27" t="n">
-        <v>12.72</v>
+        <v>388.2359796501235</v>
       </c>
       <c r="E27" t="n">
-        <v>12.72</v>
+        <v>388.2359796501235</v>
       </c>
       <c r="F27" t="n">
-        <v>12.72</v>
+        <v>388.2359796501235</v>
       </c>
       <c r="G27" t="n">
-        <v>12.72</v>
+        <v>227.6299190440582</v>
       </c>
       <c r="H27" t="n">
-        <v>12.72</v>
+        <v>67.02385843799262</v>
       </c>
       <c r="I27" t="n">
         <v>12.72</v>
       </c>
       <c r="J27" t="n">
-        <v>170.13</v>
+        <v>108.382248779996</v>
       </c>
       <c r="K27" t="n">
-        <v>322.7295263113208</v>
+        <v>265.7922487799959</v>
       </c>
       <c r="L27" t="n">
-        <v>478.59</v>
+        <v>423.2022487799959</v>
       </c>
       <c r="M27" t="n">
-        <v>478.59</v>
+        <v>423.2022487799959</v>
       </c>
       <c r="N27" t="n">
-        <v>478.59</v>
+        <v>471.1970253469769</v>
       </c>
       <c r="O27" t="n">
-        <v>478.59</v>
+        <v>628.6070253469769</v>
       </c>
       <c r="P27" t="n">
         <v>636</v>
@@ -6326,22 +6326,22 @@
         <v>636</v>
       </c>
       <c r="T27" t="n">
-        <v>475.3939393939381</v>
+        <v>636</v>
       </c>
       <c r="U27" t="n">
-        <v>475.3939393939381</v>
+        <v>636</v>
       </c>
       <c r="V27" t="n">
-        <v>333.9321212121217</v>
+        <v>475.393939393936</v>
       </c>
       <c r="W27" t="n">
-        <v>333.9321212121217</v>
+        <v>475.393939393936</v>
       </c>
       <c r="X27" t="n">
-        <v>333.9321212121217</v>
+        <v>388.2359796501235</v>
       </c>
       <c r="Y27" t="n">
-        <v>333.9321212121217</v>
+        <v>388.2359796501235</v>
       </c>
     </row>
     <row r="28">
@@ -6384,31 +6384,31 @@
         <v>154.0833840950743</v>
       </c>
       <c r="M28" t="n">
-        <v>12.72</v>
+        <v>154.0833840950743</v>
       </c>
       <c r="N28" t="n">
-        <v>12.72</v>
+        <v>154.0833840950743</v>
       </c>
       <c r="O28" t="n">
-        <v>12.72</v>
+        <v>154.0833840950743</v>
       </c>
       <c r="P28" t="n">
-        <v>12.72</v>
+        <v>154.0833840950743</v>
       </c>
       <c r="Q28" t="n">
-        <v>12.72</v>
+        <v>154.0833840950743</v>
       </c>
       <c r="R28" t="n">
-        <v>12.72</v>
+        <v>154.0833840950743</v>
       </c>
       <c r="S28" t="n">
-        <v>12.72</v>
+        <v>143.0304710682703</v>
       </c>
       <c r="T28" t="n">
-        <v>12.72</v>
+        <v>77.46914374782452</v>
       </c>
       <c r="U28" t="n">
-        <v>12.72</v>
+        <v>69.45768708708707</v>
       </c>
       <c r="V28" t="n">
         <v>12.72</v>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>173.3260606060612</v>
+        <v>12.72</v>
       </c>
       <c r="C29" t="n">
-        <v>173.3260606060612</v>
+        <v>12.72</v>
       </c>
       <c r="D29" t="n">
         <v>12.72</v>
@@ -6466,10 +6466,10 @@
         <v>367.5503861289184</v>
       </c>
       <c r="N29" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="O29" t="n">
-        <v>478.8976957216814</v>
+        <v>478.8976957216815</v>
       </c>
       <c r="P29" t="n">
         <v>636</v>
@@ -6484,22 +6484,22 @@
         <v>636</v>
       </c>
       <c r="T29" t="n">
-        <v>475.393939393938</v>
+        <v>475.3939393939311</v>
       </c>
       <c r="U29" t="n">
-        <v>475.393939393938</v>
+        <v>475.3939393939311</v>
       </c>
       <c r="V29" t="n">
-        <v>475.393939393938</v>
+        <v>314.7878787878633</v>
       </c>
       <c r="W29" t="n">
-        <v>475.393939393938</v>
+        <v>173.3260606060673</v>
       </c>
       <c r="X29" t="n">
-        <v>333.9321212121224</v>
+        <v>12.72</v>
       </c>
       <c r="Y29" t="n">
-        <v>173.3260606060612</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="30">
@@ -6509,46 +6509,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="C30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="D30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="E30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="F30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="G30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="H30" t="n">
-        <v>12.72</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="I30" t="n">
         <v>12.72</v>
       </c>
       <c r="J30" t="n">
-        <v>12.72</v>
+        <v>170.13</v>
       </c>
       <c r="K30" t="n">
         <v>170.13</v>
       </c>
       <c r="L30" t="n">
-        <v>327.54</v>
+        <v>184.4204736886793</v>
       </c>
       <c r="M30" t="n">
-        <v>327.54</v>
+        <v>321.1800000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>327.54</v>
+        <v>321.1800000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>484.9499999999999</v>
+        <v>478.59</v>
       </c>
       <c r="P30" t="n">
         <v>636</v>
@@ -6557,28 +6557,28 @@
         <v>636</v>
       </c>
       <c r="R30" t="n">
-        <v>636</v>
+        <v>475.3939393939307</v>
       </c>
       <c r="S30" t="n">
-        <v>636</v>
+        <v>314.7878787878618</v>
       </c>
       <c r="T30" t="n">
-        <v>475.3939393939378</v>
+        <v>154.1818181817931</v>
       </c>
       <c r="U30" t="n">
-        <v>475.3939393939378</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="V30" t="n">
-        <v>314.7878787878768</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="W30" t="n">
-        <v>314.7878787878768</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="X30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.1818181818157</v>
+        <v>27.62991904405321</v>
       </c>
     </row>
     <row r="31">
@@ -6609,7 +6609,7 @@
         <v>12.72</v>
       </c>
       <c r="I31" t="n">
-        <v>32.79686254264028</v>
+        <v>32.79686254264029</v>
       </c>
       <c r="J31" t="n">
         <v>190.2068625426403</v>
@@ -6648,16 +6648,16 @@
         <v>194.7974459429451</v>
       </c>
       <c r="V31" t="n">
-        <v>194.7974459429451</v>
+        <v>177.4536982497975</v>
       </c>
       <c r="W31" t="n">
-        <v>149.9764259038444</v>
+        <v>132.6326782106968</v>
       </c>
       <c r="X31" t="n">
-        <v>83.87173355020045</v>
+        <v>132.6326782106968</v>
       </c>
       <c r="Y31" t="n">
-        <v>83.87173355020045</v>
+        <v>118.8955558960391</v>
       </c>
     </row>
     <row r="32">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>173.3260606060614</v>
+        <v>333.9321212121334</v>
       </c>
       <c r="C32" t="n">
-        <v>173.3260606060614</v>
+        <v>173.3260606060667</v>
       </c>
       <c r="D32" t="n">
-        <v>173.3260606060614</v>
+        <v>12.72</v>
       </c>
       <c r="E32" t="n">
         <v>12.72</v>
@@ -6700,13 +6700,13 @@
         <v>367.5503861289183</v>
       </c>
       <c r="M32" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="N32" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="O32" t="n">
-        <v>478.8976957216814</v>
+        <v>478.8976957216815</v>
       </c>
       <c r="P32" t="n">
         <v>636</v>
@@ -6718,25 +6718,25 @@
         <v>636</v>
       </c>
       <c r="S32" t="n">
-        <v>475.3939393939376</v>
+        <v>475.3939393939313</v>
       </c>
       <c r="T32" t="n">
-        <v>475.3939393939376</v>
+        <v>475.3939393939313</v>
       </c>
       <c r="U32" t="n">
-        <v>475.3939393939376</v>
+        <v>475.3939393939313</v>
       </c>
       <c r="V32" t="n">
-        <v>475.3939393939376</v>
+        <v>475.3939393939313</v>
       </c>
       <c r="W32" t="n">
-        <v>475.3939393939376</v>
+        <v>475.3939393939313</v>
       </c>
       <c r="X32" t="n">
-        <v>333.9321212121229</v>
+        <v>475.3939393939313</v>
       </c>
       <c r="Y32" t="n">
-        <v>173.3260606060614</v>
+        <v>475.3939393939313</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>314.7878787878761</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="C33" t="n">
-        <v>173.3260606060614</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="D33" t="n">
-        <v>12.72</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="E33" t="n">
-        <v>12.72</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="F33" t="n">
-        <v>12.72</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="G33" t="n">
-        <v>12.72</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="H33" t="n">
-        <v>12.72</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="I33" t="n">
         <v>12.72</v>
@@ -6773,22 +6773,22 @@
         <v>170.13</v>
       </c>
       <c r="K33" t="n">
-        <v>306.8895263113208</v>
+        <v>170.13</v>
       </c>
       <c r="L33" t="n">
-        <v>321.1800000000001</v>
+        <v>313.7427126182943</v>
       </c>
       <c r="M33" t="n">
-        <v>321.1800000000001</v>
+        <v>313.7427126182943</v>
       </c>
       <c r="N33" t="n">
-        <v>321.1800000000001</v>
+        <v>313.7427126182943</v>
       </c>
       <c r="O33" t="n">
-        <v>478.59</v>
+        <v>471.1527126182942</v>
       </c>
       <c r="P33" t="n">
-        <v>636</v>
+        <v>628.5627126182943</v>
       </c>
       <c r="Q33" t="n">
         <v>636</v>
@@ -6800,22 +6800,22 @@
         <v>636</v>
       </c>
       <c r="T33" t="n">
-        <v>475.3939393939376</v>
+        <v>475.3939393939312</v>
       </c>
       <c r="U33" t="n">
-        <v>475.3939393939376</v>
+        <v>314.7878787878631</v>
       </c>
       <c r="V33" t="n">
-        <v>475.3939393939376</v>
+        <v>154.1818181817964</v>
       </c>
       <c r="W33" t="n">
-        <v>475.3939393939376</v>
+        <v>154.1818181817964</v>
       </c>
       <c r="X33" t="n">
-        <v>314.7878787878761</v>
+        <v>27.62991904405321</v>
       </c>
       <c r="Y33" t="n">
-        <v>314.7878787878761</v>
+        <v>27.62991904405321</v>
       </c>
     </row>
     <row r="34">
@@ -6825,22 +6825,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>112.7007119565218</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="C34" t="n">
-        <v>112.7007119565218</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="D34" t="n">
-        <v>112.7007119565218</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="E34" t="n">
-        <v>12.72</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="F34" t="n">
-        <v>12.72</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="G34" t="n">
-        <v>12.72</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="H34" t="n">
         <v>12.72</v>
@@ -6861,40 +6861,40 @@
         <v>190.2068625426403</v>
       </c>
       <c r="N34" t="n">
-        <v>188.1182965257496</v>
+        <v>190.2068625426403</v>
       </c>
       <c r="O34" t="n">
-        <v>188.1182965257496</v>
+        <v>190.2068625426403</v>
       </c>
       <c r="P34" t="n">
-        <v>188.1182965257496</v>
+        <v>190.2068625426403</v>
       </c>
       <c r="Q34" t="n">
-        <v>188.1182965257496</v>
+        <v>113.0841941381819</v>
       </c>
       <c r="R34" t="n">
-        <v>188.1182965257496</v>
+        <v>113.0841941381819</v>
       </c>
       <c r="S34" t="n">
-        <v>188.1182965257496</v>
+        <v>113.0841941381819</v>
       </c>
       <c r="T34" t="n">
-        <v>188.1182965257496</v>
+        <v>86.91680621167552</v>
       </c>
       <c r="U34" t="n">
-        <v>218.8762678525608</v>
+        <v>117.6747775384868</v>
       </c>
       <c r="V34" t="n">
-        <v>218.8762678525608</v>
+        <v>100.3310298453391</v>
       </c>
       <c r="W34" t="n">
-        <v>218.8762678525608</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="X34" t="n">
-        <v>218.8762678525608</v>
+        <v>55.51000980623838</v>
       </c>
       <c r="Y34" t="n">
-        <v>218.8762678525608</v>
+        <v>55.51000980623838</v>
       </c>
     </row>
     <row r="35">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>333.932121212124</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="C35" t="n">
-        <v>333.932121212124</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="D35" t="n">
-        <v>173.3260606060624</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="E35" t="n">
-        <v>173.3260606060624</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="F35" t="n">
-        <v>173.3260606060624</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="G35" t="n">
-        <v>173.3260606060624</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="H35" t="n">
         <v>12.72</v>
@@ -6937,13 +6937,13 @@
         <v>367.5503861289183</v>
       </c>
       <c r="M35" t="n">
-        <v>364.0368064492792</v>
+        <v>367.5503861289184</v>
       </c>
       <c r="N35" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="O35" t="n">
-        <v>478.8976957216814</v>
+        <v>478.8976957216815</v>
       </c>
       <c r="P35" t="n">
         <v>636</v>
@@ -6961,19 +6961,19 @@
         <v>636</v>
       </c>
       <c r="U35" t="n">
-        <v>494.5381818181855</v>
+        <v>475.3939393939322</v>
       </c>
       <c r="V35" t="n">
-        <v>333.932121212124</v>
+        <v>314.7878787878656</v>
       </c>
       <c r="W35" t="n">
-        <v>333.932121212124</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="X35" t="n">
-        <v>333.932121212124</v>
+        <v>154.1818181817987</v>
       </c>
       <c r="Y35" t="n">
-        <v>333.932121212124</v>
+        <v>154.1818181817987</v>
       </c>
     </row>
     <row r="36">
@@ -6983,49 +6983,49 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>475.3939393939375</v>
+        <v>477.3669090605244</v>
       </c>
       <c r="C36" t="n">
-        <v>317.9200267081476</v>
+        <v>477.3669090605244</v>
       </c>
       <c r="D36" t="n">
-        <v>317.9200267081476</v>
+        <v>477.3669090605244</v>
       </c>
       <c r="E36" t="n">
-        <v>157.313966102086</v>
+        <v>477.3669090605244</v>
       </c>
       <c r="F36" t="n">
-        <v>157.313966102086</v>
+        <v>318.1383814465074</v>
       </c>
       <c r="G36" t="n">
-        <v>12.72</v>
+        <v>173.5444153444214</v>
       </c>
       <c r="H36" t="n">
-        <v>12.72</v>
+        <v>27.62991904405322</v>
       </c>
       <c r="I36" t="n">
         <v>12.72</v>
       </c>
       <c r="J36" t="n">
-        <v>12.72</v>
+        <v>149.4795263113208</v>
       </c>
       <c r="K36" t="n">
-        <v>170.13</v>
+        <v>149.4795263113208</v>
       </c>
       <c r="L36" t="n">
-        <v>184.4204736886793</v>
+        <v>163.7700000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>306.3497379652709</v>
+        <v>321.1800000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>463.7597379652709</v>
+        <v>321.1800000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>621.1697379652709</v>
+        <v>478.59</v>
       </c>
       <c r="P36" t="n">
-        <v>628.562712618294</v>
+        <v>636</v>
       </c>
       <c r="Q36" t="n">
         <v>636</v>
@@ -7037,22 +7037,22 @@
         <v>636</v>
       </c>
       <c r="T36" t="n">
-        <v>475.3939393939375</v>
+        <v>636</v>
       </c>
       <c r="U36" t="n">
-        <v>475.3939393939375</v>
+        <v>636</v>
       </c>
       <c r="V36" t="n">
-        <v>475.3939393939375</v>
+        <v>636</v>
       </c>
       <c r="W36" t="n">
-        <v>475.3939393939375</v>
+        <v>636</v>
       </c>
       <c r="X36" t="n">
-        <v>475.3939393939375</v>
+        <v>477.3669090605244</v>
       </c>
       <c r="Y36" t="n">
-        <v>475.3939393939375</v>
+        <v>477.3669090605244</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="C37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="D37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="E37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="F37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="G37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="H37" t="n">
+        <v>26.13422363366357</v>
+      </c>
+      <c r="I37" t="n">
+        <v>46.21108617630385</v>
+      </c>
+      <c r="J37" t="n">
+        <v>203.6210861763038</v>
+      </c>
+      <c r="K37" t="n">
+        <v>203.6210861763038</v>
+      </c>
+      <c r="L37" t="n">
+        <v>203.6210861763038</v>
+      </c>
+      <c r="M37" t="n">
+        <v>203.6210861763038</v>
+      </c>
+      <c r="N37" t="n">
+        <v>203.6210861763038</v>
+      </c>
+      <c r="O37" t="n">
+        <v>203.6210861763038</v>
+      </c>
+      <c r="P37" t="n">
+        <v>203.6210861763038</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>199.493448532567</v>
+      </c>
+      <c r="R37" t="n">
+        <v>38.8873879265064</v>
+      </c>
+      <c r="S37" t="n">
+        <v>38.8873879265064</v>
+      </c>
+      <c r="T37" t="n">
         <v>12.72</v>
       </c>
-      <c r="I37" t="n">
-        <v>32.79686254264028</v>
-      </c>
-      <c r="J37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="K37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="L37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="M37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="N37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="O37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="P37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>190.2068625426403</v>
-      </c>
-      <c r="R37" t="n">
-        <v>185.3580990854878</v>
-      </c>
-      <c r="S37" t="n">
-        <v>24.75203847942715</v>
-      </c>
-      <c r="T37" t="n">
-        <v>24.75203847942715</v>
-      </c>
       <c r="U37" t="n">
-        <v>55.51000980623839</v>
+        <v>43.47797132681124</v>
       </c>
       <c r="V37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="W37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="X37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
       <c r="Y37" t="n">
-        <v>55.51000980623839</v>
+        <v>26.13422363366357</v>
       </c>
     </row>
     <row r="38">
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>154.1818181818154</v>
+        <v>154.1818181818007</v>
       </c>
       <c r="C38" t="n">
-        <v>154.1818181818154</v>
+        <v>154.1818181818007</v>
       </c>
       <c r="D38" t="n">
-        <v>154.1818181818154</v>
+        <v>154.1818181818007</v>
       </c>
       <c r="E38" t="n">
-        <v>154.1818181818154</v>
+        <v>154.1818181818007</v>
       </c>
       <c r="F38" t="n">
-        <v>154.1818181818154</v>
+        <v>12.72</v>
       </c>
       <c r="G38" t="n">
         <v>12.72</v>
@@ -7177,10 +7177,10 @@
         <v>367.5503861289184</v>
       </c>
       <c r="N38" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492794</v>
       </c>
       <c r="O38" t="n">
-        <v>478.8976957216814</v>
+        <v>478.8976957216817</v>
       </c>
       <c r="P38" t="n">
         <v>636</v>
@@ -7198,19 +7198,19 @@
         <v>636</v>
       </c>
       <c r="U38" t="n">
-        <v>636</v>
+        <v>475.3939393939324</v>
       </c>
       <c r="V38" t="n">
-        <v>636</v>
+        <v>314.7878787878665</v>
       </c>
       <c r="W38" t="n">
-        <v>475.3939393939386</v>
+        <v>154.1818181818007</v>
       </c>
       <c r="X38" t="n">
-        <v>475.3939393939386</v>
+        <v>154.1818181818007</v>
       </c>
       <c r="Y38" t="n">
-        <v>314.787878787877</v>
+        <v>154.1818181818007</v>
       </c>
     </row>
     <row r="39">
@@ -7220,43 +7220,43 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>317.9200267081475</v>
+        <v>186.8584466580703</v>
       </c>
       <c r="C39" t="n">
-        <v>317.9200267081475</v>
+        <v>186.8584466580703</v>
       </c>
       <c r="D39" t="n">
-        <v>157.3139661020859</v>
+        <v>186.8584466580703</v>
       </c>
       <c r="E39" t="n">
-        <v>157.3139661020859</v>
+        <v>186.8584466580703</v>
       </c>
       <c r="F39" t="n">
-        <v>157.3139661020859</v>
+        <v>27.62991904405322</v>
       </c>
       <c r="G39" t="n">
-        <v>12.72</v>
+        <v>27.62991904405322</v>
       </c>
       <c r="H39" t="n">
-        <v>12.72</v>
+        <v>27.62991904405322</v>
       </c>
       <c r="I39" t="n">
         <v>12.72</v>
       </c>
       <c r="J39" t="n">
-        <v>12.72</v>
+        <v>170.13</v>
       </c>
       <c r="K39" t="n">
-        <v>170.13</v>
+        <v>299.4965516582977</v>
       </c>
       <c r="L39" t="n">
-        <v>184.4204736886793</v>
+        <v>313.787025346977</v>
       </c>
       <c r="M39" t="n">
-        <v>341.8304736886793</v>
+        <v>313.787025346977</v>
       </c>
       <c r="N39" t="n">
-        <v>499.2404736886792</v>
+        <v>471.1970253469769</v>
       </c>
       <c r="O39" t="n">
         <v>628.6070253469769</v>
@@ -7274,22 +7274,22 @@
         <v>636</v>
       </c>
       <c r="T39" t="n">
-        <v>636</v>
+        <v>475.393939393933</v>
       </c>
       <c r="U39" t="n">
-        <v>636</v>
+        <v>475.393939393933</v>
       </c>
       <c r="V39" t="n">
-        <v>636</v>
+        <v>347.4645072641365</v>
       </c>
       <c r="W39" t="n">
-        <v>636</v>
+        <v>347.4645072641365</v>
       </c>
       <c r="X39" t="n">
-        <v>636</v>
+        <v>186.8584466580703</v>
       </c>
       <c r="Y39" t="n">
-        <v>475.3939393939386</v>
+        <v>186.8584466580703</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>147.1516730870916</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="C40" t="n">
-        <v>55.51000980623838</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="D40" t="n">
-        <v>55.51000980623838</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="E40" t="n">
-        <v>55.51000980623838</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="F40" t="n">
-        <v>55.51000980623838</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="G40" t="n">
-        <v>55.51000980623838</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="H40" t="n">
         <v>12.72</v>
       </c>
       <c r="I40" t="n">
-        <v>32.79686254264029</v>
+        <v>32.79686254264028</v>
       </c>
       <c r="J40" t="n">
         <v>190.2068625426403</v>
@@ -7341,34 +7341,34 @@
         <v>190.2068625426403</v>
       </c>
       <c r="P40" t="n">
-        <v>190.2068625426403</v>
+        <v>113.0841941381819</v>
       </c>
       <c r="Q40" t="n">
-        <v>142.5610896867867</v>
+        <v>113.0841941381819</v>
       </c>
       <c r="R40" t="n">
-        <v>142.5610896867867</v>
+        <v>113.0841941381819</v>
       </c>
       <c r="S40" t="n">
-        <v>142.5610896867867</v>
+        <v>113.0841941381819</v>
       </c>
       <c r="T40" t="n">
-        <v>116.3937017602804</v>
+        <v>86.91680621167552</v>
       </c>
       <c r="U40" t="n">
-        <v>147.1516730870916</v>
+        <v>117.6747775384868</v>
       </c>
       <c r="V40" t="n">
-        <v>147.1516730870916</v>
+        <v>100.3310298453391</v>
       </c>
       <c r="W40" t="n">
-        <v>147.1516730870916</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="X40" t="n">
-        <v>147.1516730870916</v>
+        <v>55.51000980623839</v>
       </c>
       <c r="Y40" t="n">
-        <v>147.1516730870916</v>
+        <v>55.51000980623839</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>154.1818181818096</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="C41" t="n">
-        <v>154.1818181818096</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="D41" t="n">
-        <v>154.1818181818096</v>
+        <v>395.1580824992099</v>
       </c>
       <c r="E41" t="n">
-        <v>154.1818181818096</v>
+        <v>395.1580824992099</v>
       </c>
       <c r="F41" t="n">
-        <v>18.23546001144225</v>
+        <v>234.5520218931489</v>
       </c>
       <c r="G41" t="n">
-        <v>18.23546001144225</v>
+        <v>73.94596128708787</v>
       </c>
       <c r="H41" t="n">
         <v>18.23546001144225</v>
@@ -7411,13 +7411,13 @@
         <v>367.5503861289183</v>
       </c>
       <c r="M41" t="n">
-        <v>364.0368064492792</v>
+        <v>367.5503861289184</v>
       </c>
       <c r="N41" t="n">
-        <v>364.0368064492792</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="O41" t="n">
-        <v>478.8976957216814</v>
+        <v>478.8976957216815</v>
       </c>
       <c r="P41" t="n">
         <v>636</v>
@@ -7426,28 +7426,28 @@
         <v>636</v>
       </c>
       <c r="R41" t="n">
-        <v>636</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="S41" t="n">
-        <v>475.3939393939362</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="T41" t="n">
-        <v>475.3939393939362</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="U41" t="n">
-        <v>314.7878787878722</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="V41" t="n">
-        <v>314.7878787878722</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="W41" t="n">
-        <v>154.1818181818096</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="X41" t="n">
-        <v>154.1818181818096</v>
+        <v>555.7641431052708</v>
       </c>
       <c r="Y41" t="n">
-        <v>154.1818181818096</v>
+        <v>555.7641431052708</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>475.3939393939374</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="C42" t="n">
-        <v>475.3939393939374</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="D42" t="n">
-        <v>475.3939393939374</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="E42" t="n">
-        <v>314.7878787878747</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="F42" t="n">
-        <v>173.3260606060634</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="G42" t="n">
-        <v>173.3260606060634</v>
+        <v>173.3260606060606</v>
       </c>
       <c r="H42" t="n">
         <v>12.72</v>
@@ -7481,25 +7481,25 @@
         <v>12.72</v>
       </c>
       <c r="J42" t="n">
-        <v>12.72</v>
+        <v>67.79224877999597</v>
       </c>
       <c r="K42" t="n">
-        <v>12.72</v>
+        <v>225.202248779996</v>
       </c>
       <c r="L42" t="n">
-        <v>127.9904736886793</v>
+        <v>239.4927224686752</v>
       </c>
       <c r="M42" t="n">
-        <v>285.4004736886793</v>
+        <v>396.9027224686752</v>
       </c>
       <c r="N42" t="n">
-        <v>442.8104736886793</v>
+        <v>396.9027224686752</v>
       </c>
       <c r="O42" t="n">
-        <v>543.3057346538432</v>
+        <v>474.20786866599</v>
       </c>
       <c r="P42" t="n">
-        <v>636</v>
+        <v>631.6178686659899</v>
       </c>
       <c r="Q42" t="n">
         <v>636</v>
@@ -7508,25 +7508,25 @@
         <v>636</v>
       </c>
       <c r="S42" t="n">
-        <v>636</v>
+        <v>475.3939393939394</v>
       </c>
       <c r="T42" t="n">
-        <v>636</v>
+        <v>475.3939393939394</v>
       </c>
       <c r="U42" t="n">
-        <v>636</v>
+        <v>475.3939393939394</v>
       </c>
       <c r="V42" t="n">
-        <v>636</v>
+        <v>475.3939393939394</v>
       </c>
       <c r="W42" t="n">
-        <v>636</v>
+        <v>475.3939393939394</v>
       </c>
       <c r="X42" t="n">
-        <v>636</v>
+        <v>475.3939393939394</v>
       </c>
       <c r="Y42" t="n">
-        <v>475.3939393939374</v>
+        <v>475.3939393939394</v>
       </c>
     </row>
     <row r="43">
@@ -7590,7 +7590,7 @@
         <v>113.4933840950743</v>
       </c>
       <c r="T43" t="n">
-        <v>62.14559807487885</v>
+        <v>12.72</v>
       </c>
       <c r="U43" t="n">
         <v>12.72</v>
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12.72</v>
+        <v>154.1818181818169</v>
       </c>
       <c r="C44" t="n">
-        <v>12.72</v>
+        <v>154.1818181818169</v>
       </c>
       <c r="D44" t="n">
-        <v>12.72</v>
+        <v>154.1818181818169</v>
       </c>
       <c r="E44" t="n">
-        <v>12.72</v>
+        <v>154.1818181818169</v>
       </c>
       <c r="F44" t="n">
-        <v>12.72</v>
+        <v>101.0637428397251</v>
       </c>
       <c r="G44" t="n">
-        <v>12.72</v>
+        <v>101.0637428397251</v>
       </c>
       <c r="H44" t="n">
-        <v>12.72</v>
+        <v>101.0637428397251</v>
       </c>
       <c r="I44" t="n">
         <v>12.72</v>
@@ -7651,10 +7651,10 @@
         <v>367.5503861289184</v>
       </c>
       <c r="N44" t="n">
-        <v>364.0368064492794</v>
+        <v>364.0368064492793</v>
       </c>
       <c r="O44" t="n">
-        <v>478.8976957216817</v>
+        <v>478.8976957216815</v>
       </c>
       <c r="P44" t="n">
         <v>636</v>
@@ -7669,22 +7669,22 @@
         <v>475.393939393939</v>
       </c>
       <c r="T44" t="n">
-        <v>475.393939393939</v>
+        <v>314.787878787878</v>
       </c>
       <c r="U44" t="n">
-        <v>475.393939393939</v>
+        <v>314.787878787878</v>
       </c>
       <c r="V44" t="n">
-        <v>314.7878787878759</v>
+        <v>154.1818181818169</v>
       </c>
       <c r="W44" t="n">
-        <v>154.1818181818129</v>
+        <v>154.1818181818169</v>
       </c>
       <c r="X44" t="n">
-        <v>12.72</v>
+        <v>154.1818181818169</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.72</v>
+        <v>154.1818181818169</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>333.9321212121271</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="C45" t="n">
-        <v>333.9321212121271</v>
+        <v>173.3260606060606</v>
       </c>
       <c r="D45" t="n">
-        <v>333.9321212121271</v>
+        <v>173.3260606060606</v>
       </c>
       <c r="E45" t="n">
-        <v>173.3260606060639</v>
+        <v>173.3260606060606</v>
       </c>
       <c r="F45" t="n">
-        <v>173.3260606060639</v>
+        <v>173.3260606060606</v>
       </c>
       <c r="G45" t="n">
-        <v>173.3260606060639</v>
+        <v>173.3260606060606</v>
       </c>
       <c r="H45" t="n">
         <v>12.72</v>
@@ -7718,52 +7718,52 @@
         <v>12.72</v>
       </c>
       <c r="J45" t="n">
-        <v>12.72</v>
+        <v>170.13</v>
       </c>
       <c r="K45" t="n">
-        <v>170.13</v>
+        <v>327.54</v>
       </c>
       <c r="L45" t="n">
-        <v>204.2204736886793</v>
+        <v>361.6304736886792</v>
       </c>
       <c r="M45" t="n">
-        <v>321.1800000000001</v>
+        <v>361.6304736886792</v>
       </c>
       <c r="N45" t="n">
-        <v>321.1800000000001</v>
+        <v>519.0404736886792</v>
       </c>
       <c r="O45" t="n">
-        <v>478.59</v>
+        <v>608.8070253469768</v>
       </c>
       <c r="P45" t="n">
         <v>636</v>
       </c>
       <c r="Q45" t="n">
-        <v>636</v>
+        <v>557.6428235220999</v>
       </c>
       <c r="R45" t="n">
-        <v>636</v>
+        <v>397.0367629160393</v>
       </c>
       <c r="S45" t="n">
-        <v>636</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="T45" t="n">
-        <v>636</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="U45" t="n">
-        <v>636</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="V45" t="n">
-        <v>494.5381818181901</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="W45" t="n">
-        <v>494.5381818181901</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="X45" t="n">
-        <v>494.5381818181901</v>
+        <v>333.9321212121213</v>
       </c>
       <c r="Y45" t="n">
-        <v>333.9321212121271</v>
+        <v>333.9321212121213</v>
       </c>
     </row>
     <row r="46">
@@ -7833,7 +7833,7 @@
         <v>32.31338409507427</v>
       </c>
       <c r="V46" t="n">
-        <v>32.31338409507427</v>
+        <v>12.72</v>
       </c>
       <c r="W46" t="n">
         <v>12.72</v>
@@ -7967,13 +7967,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>365.3727386934673</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>833.7385838818576</v>
+        <v>693.1113225753247</v>
       </c>
       <c r="N2" t="n">
         <v>785.9868977683277</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>53.43813658879195</v>
+        <v>559.438136588792</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8207,22 +8207,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>331.5394472361809</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>636.2821718550234</v>
+        <v>856.14114774282</v>
       </c>
       <c r="N5" t="n">
-        <v>279.9868977683277</v>
+        <v>785.9868977683277</v>
       </c>
       <c r="O5" t="n">
-        <v>389.9788997248462</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>347.3108037592743</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>53.43813658879195</v>
+        <v>396.4083114212969</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8283,10 +8283,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K6" t="n">
-        <v>295.8802408630135</v>
+        <v>295.0948415008565</v>
       </c>
       <c r="L6" t="n">
-        <v>387.3039370976412</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M6" t="n">
         <v>471.6948204301074</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>111.6804713483844</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>350.1411477428198</v>
       </c>
       <c r="N8" t="n">
-        <v>279.9868977683277</v>
+        <v>698.6523360146761</v>
       </c>
       <c r="O8" t="n">
-        <v>389.9788997248462</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>347.3108037592743</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>559.438136588792</v>
@@ -8520,7 +8520,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>295.8802408630135</v>
+        <v>295.0948415008565</v>
       </c>
       <c r="L9" t="n">
         <v>388.0893364597981</v>
@@ -8532,7 +8532,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O9" t="n">
-        <v>381.8963994387467</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
         <v>219.1507118405495</v>
@@ -8672,13 +8672,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>11.10732113510807</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>201.6654382463485</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>856.14114774282</v>
       </c>
       <c r="N11" t="n">
-        <v>279.9868977683277</v>
+        <v>336.5461397517857</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,10 +8696,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27.54003465557064</v>
+        <v>53.43813658879195</v>
       </c>
       <c r="R11" t="n">
-        <v>258.9746146601419</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J12" t="n">
         <v>227.4647419277884</v>
@@ -8760,7 +8760,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L12" t="n">
-        <v>388.0893364597981</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>234.8697782656032</v>
@@ -8769,13 +8769,13 @@
         <v>196.9402317796766</v>
       </c>
       <c r="O12" t="n">
-        <v>289.4896353887233</v>
+        <v>374.8054612180318</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>127.451827871478</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>331.5394472361809</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>350.1411477428198</v>
+        <v>856.14114774282</v>
       </c>
       <c r="N14" t="n">
         <v>279.9868977683277</v>
       </c>
       <c r="O14" t="n">
-        <v>389.9788997248462</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>559.438136588792</v>
+        <v>122.6356059897777</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -8988,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J15" t="n">
         <v>227.4647419277884</v>
@@ -9000,19 +9000,19 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M15" t="n">
-        <v>334.4577438194912</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O15" t="n">
-        <v>382.6817988009037</v>
+        <v>381.1100762755821</v>
       </c>
       <c r="P15" t="n">
         <v>219.1507118405495</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -9146,31 +9146,31 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>120.6470157237802</v>
+        <v>86.23247010105115</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>365.3727386934675</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>331.5394472361809</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>350.1411477428198</v>
+        <v>856.14114774282</v>
       </c>
       <c r="N17" t="n">
-        <v>279.9868977683277</v>
+        <v>785.9868977683277</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>193.3387066939705</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>53.43813658879195</v>
+        <v>396.4083114212969</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9234,7 +9234,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L18" t="n">
-        <v>95.73095951145807</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M18" t="n">
         <v>471.6948204301074</v>
@@ -9243,7 +9243,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>382.6817988009037</v>
+        <v>90.32342185256367</v>
       </c>
       <c r="P18" t="n">
         <v>219.1507118405495</v>
@@ -9383,10 +9383,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>120.6470157237802</v>
+        <v>102.8142292180315</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9395,16 +9395,16 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>350.1411477428198</v>
+        <v>768.8065859891682</v>
       </c>
       <c r="N20" t="n">
-        <v>785.9868977683277</v>
+        <v>279.9868977683277</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>325.1373883267568</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>559.438136588792</v>
@@ -9477,10 +9477,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N21" t="n">
-        <v>485.4085271713503</v>
+        <v>396.8963013044536</v>
       </c>
       <c r="O21" t="n">
-        <v>294.1695729340069</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -9620,25 +9620,25 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>120.6470157237802</v>
+        <v>102.8142292180317</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>365.3727386934675</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>350.1411477428198</v>
+        <v>403.4338472957007</v>
       </c>
       <c r="N23" t="n">
-        <v>721.1453863702384</v>
+        <v>279.9868977683277</v>
       </c>
       <c r="O23" t="n">
-        <v>389.9788997248462</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -9708,19 +9708,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L24" t="n">
-        <v>368.8946941440258</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M24" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N24" t="n">
-        <v>196.9402317796766</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O24" t="n">
-        <v>382.6817988009037</v>
+        <v>294.1695729340069</v>
       </c>
       <c r="P24" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>17.27519534353338</v>
@@ -9869,10 +9869,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>203.6627038599771</v>
+        <v>346.6627038599772</v>
       </c>
       <c r="N26" t="n">
-        <v>136.9868977683277</v>
+        <v>279.9868977683277</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>53.43813658879195</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,25 +9939,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>205.371465878792</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>163.4015200034306</v>
+        <v>25.26058433542974</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.565178092243173</v>
       </c>
       <c r="M27" t="n">
-        <v>184.539507329381</v>
+        <v>119.2924395824978</v>
       </c>
       <c r="N27" t="n">
-        <v>196.9402317796766</v>
+        <v>102.4198040695564</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4896353887233715</v>
+        <v>16.48963538872337</v>
       </c>
       <c r="P27" t="n">
-        <v>151.5323488353302</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10094,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>116.6454297004272</v>
+        <v>117.2119313746454</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -10109,7 +10109,7 @@
         <v>350.1411477428198</v>
       </c>
       <c r="N29" t="n">
-        <v>276.5084538854849</v>
+        <v>276.508453885485</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         <v>53.43813658879195</v>
       </c>
       <c r="R29" t="n">
-        <v>294.54111633436</v>
+        <v>293.974614660141</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -10176,16 +10176,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J30" t="n">
-        <v>46.37146587879195</v>
+        <v>205.371465878792</v>
       </c>
       <c r="K30" t="n">
-        <v>168.2605843354297</v>
+        <v>9.260584335429741</v>
       </c>
       <c r="L30" t="n">
-        <v>144.5651780922432</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>234.8697782656032</v>
+        <v>373.010713933604</v>
       </c>
       <c r="N30" t="n">
         <v>196.9402317796766</v>
@@ -10194,7 +10194,7 @@
         <v>159.4896353887233</v>
       </c>
       <c r="P30" t="n">
-        <v>145.1081064110879</v>
+        <v>151.5323488353302</v>
       </c>
       <c r="Q30" t="n">
         <v>17.27519534353338</v>
@@ -10331,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>116.645429700427</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>346.6627038599771</v>
+        <v>346.6627038599772</v>
       </c>
       <c r="N32" t="n">
         <v>279.9868977683277</v>
@@ -10416,10 +10416,10 @@
         <v>205.371465878792</v>
       </c>
       <c r="K33" t="n">
-        <v>147.4015200034305</v>
+        <v>9.260584335429741</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>130.6285241713283</v>
       </c>
       <c r="M33" t="n">
         <v>234.8697782656032</v>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>120.6470157237802</v>
+        <v>117.2119313746459</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>346.6627038599771</v>
+        <v>350.1411477428198</v>
       </c>
       <c r="N35" t="n">
-        <v>279.9868977683277</v>
+        <v>276.508453885485</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10595,7 +10595,7 @@
         <v>53.43813658879195</v>
       </c>
       <c r="R35" t="n">
-        <v>294.54111633436</v>
+        <v>293.9746146601414</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -10650,25 +10650,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>46.37146587879195</v>
+        <v>184.5124015467928</v>
       </c>
       <c r="K36" t="n">
-        <v>168.2605843354297</v>
+        <v>9.260584335429741</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>358.0306512722615</v>
+        <v>393.8697782656031</v>
       </c>
       <c r="N36" t="n">
-        <v>355.9402317796765</v>
+        <v>196.9402317796766</v>
       </c>
       <c r="O36" t="n">
         <v>159.4896353887233</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>151.5323488353302</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10805,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>116.6454297004264</v>
+        <v>116.6454297004272</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>350.1411477428198</v>
       </c>
       <c r="N38" t="n">
-        <v>276.5084538854849</v>
+        <v>276.5084538854852</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10887,22 +10887,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>46.37146587879195</v>
+        <v>205.371465878792</v>
       </c>
       <c r="K39" t="n">
-        <v>168.2605843354297</v>
+        <v>139.9338688387607</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>393.8697782656031</v>
+        <v>234.8697782656032</v>
       </c>
       <c r="N39" t="n">
         <v>355.9402317796765</v>
       </c>
       <c r="O39" t="n">
-        <v>131.1629198920544</v>
+        <v>159.4896353887233</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>346.6627038599771</v>
+        <v>350.1411477428198</v>
       </c>
       <c r="N41" t="n">
-        <v>225.3838254239454</v>
+        <v>276.508453885485</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>53.43813658879195</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11127,22 +11127,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>66.26058433542971</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>393.8697782656031</v>
+        <v>291.8697782656031</v>
       </c>
       <c r="N42" t="n">
-        <v>253.9402317796766</v>
+        <v>94.94023177967657</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>28.53790579958066</v>
       </c>
       <c r="P42" t="n">
-        <v>86.16291989205429</v>
+        <v>49.5323488353302</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11294,7 +11294,7 @@
         <v>350.1411477428198</v>
       </c>
       <c r="N44" t="n">
-        <v>259.322524237244</v>
+        <v>276.508453885485</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>33.43813658879195</v>
+        <v>53.43813658879195</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,25 +11361,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>46.37146587879195</v>
+        <v>205.371465878792</v>
       </c>
       <c r="K45" t="n">
-        <v>168.2605843354297</v>
+        <v>148.2605843354297</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>353.010713933604</v>
+        <v>214.8697782656032</v>
       </c>
       <c r="N45" t="n">
-        <v>176.9402317796766</v>
+        <v>346.1289110249596</v>
       </c>
       <c r="O45" t="n">
-        <v>159.4896353887233</v>
+        <v>71.16291989205435</v>
       </c>
       <c r="P45" t="n">
-        <v>151.5323488353302</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.84477126282647</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22575,13 +22575,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>132.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>192.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>19.0020495265165</v>
       </c>
     </row>
     <row r="3">
@@ -22639,7 +22639,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>217.9885276657261</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -22691,7 +22691,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>161.7203408660199</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -22706,10 +22706,10 @@
         <v>42.89677533697613</v>
       </c>
       <c r="N4" t="n">
-        <v>95.2985998618488</v>
+        <v>495.2985998618488</v>
       </c>
       <c r="O4" t="n">
-        <v>170.3521214560641</v>
+        <v>503.3907043372596</v>
       </c>
       <c r="P4" t="n">
         <v>227.4708481479496</v>
@@ -22718,10 +22718,10 @@
         <v>284.314266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>304.3045869975446</v>
+        <v>704.3045869975446</v>
       </c>
       <c r="S4" t="n">
-        <v>353.7312665881013</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -22733,7 +22733,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -22797,16 +22797,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>166.3141513624134</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>75.83613449238298</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1328543375554</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -22818,7 +22818,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22876,7 +22876,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>110.5483255942661</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -22891,7 +22891,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -22940,22 +22940,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>42.89677533697613</v>
+        <v>294.0166030634857</v>
       </c>
       <c r="N7" t="n">
-        <v>95.29859986184881</v>
+        <v>495.2985998618488</v>
       </c>
       <c r="O7" t="n">
-        <v>170.3521214560641</v>
+        <v>570.3521214560641</v>
       </c>
       <c r="P7" t="n">
-        <v>227.4708481479496</v>
+        <v>627.4708481479496</v>
       </c>
       <c r="Q7" t="n">
-        <v>284.314266425598</v>
+        <v>684.314266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>304.3045869975445</v>
+        <v>704.3045869975446</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23049,7 +23049,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>15.19912019841874</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -23110,7 +23110,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>97.57360471312109</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -23122,13 +23122,13 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>400.1714446658471</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -23150,10 +23150,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -23171,16 +23171,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>230.9060197027824</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>349.8205789774513</v>
       </c>
       <c r="M10" t="n">
-        <v>42.89677533697613</v>
+        <v>232.3090995463005</v>
       </c>
       <c r="N10" t="n">
-        <v>95.29859986184881</v>
+        <v>495.2985998618488</v>
       </c>
       <c r="O10" t="n">
         <v>170.3521214560641</v>
@@ -23189,10 +23189,10 @@
         <v>227.4708481479496</v>
       </c>
       <c r="Q10" t="n">
-        <v>284.314266425598</v>
+        <v>684.314266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>304.3045869975445</v>
+        <v>704.3045869975446</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23226,7 +23226,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>232.4745782429939</v>
       </c>
       <c r="D11" t="n">
         <v>193.3391557398498</v>
@@ -23235,10 +23235,10 @@
         <v>187.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>187.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>35.87249738598359</v>
+        <v>185.6518446488253</v>
       </c>
       <c r="H11" t="n">
         <v>179.6876737789043</v>
@@ -23277,19 +23277,19 @@
         <v>252.6559567470465</v>
       </c>
       <c r="T11" t="n">
-        <v>364.836134492383</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>432.1328543375554</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>412.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>189.2562439099348</v>
       </c>
       <c r="X11" t="n">
-        <v>375.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -23305,7 +23305,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>119.8967302945744</v>
+        <v>112.1040274107918</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>122.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>108.1480264410651</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -23353,7 +23353,7 @@
         <v>293.5483255942661</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>238.5769716627245</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -23384,16 +23384,16 @@
         <v>70.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>20.50791285469912</v>
+        <v>55.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>68.53621805555548</v>
+        <v>23.11064388529324</v>
       </c>
       <c r="E13" t="n">
-        <v>63.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>57.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -23408,16 +23408,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>13.9060197027824</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>132.8205789774513</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>225.8967753369761</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>278.2985998618488</v>
       </c>
       <c r="O13" t="n">
         <v>353.3521214560641</v>
@@ -23460,25 +23460,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>221.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>189.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>144.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>144.8896287080119</v>
       </c>
       <c r="G14" t="n">
         <v>142.6518446488253</v>
       </c>
       <c r="H14" t="n">
-        <v>136.6876737789043</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,16 +23511,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>209.6559567470465</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>304.2919302001257</v>
       </c>
       <c r="U14" t="n">
-        <v>329.1868420289046</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>369.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -23624,13 +23624,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>25.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>20.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>14.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -23660,16 +23660,16 @@
         <v>310.3521214560641</v>
       </c>
       <c r="P16" t="n">
-        <v>229.071684151767</v>
+        <v>367.4708481479496</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>424.314266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>444.3045869975445</v>
+        <v>63.68775487358147</v>
       </c>
       <c r="S16" t="n">
-        <v>93.73126658810133</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>27.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>154.459353541478</v>
       </c>
       <c r="D17" t="n">
         <v>131.3391557398498</v>
@@ -23709,13 +23709,13 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>125.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>123.6518446488253</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>36.5598826631946</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23748,10 +23748,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>190.6559567470465</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>302.836134492383</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>313.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>232.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23888,25 +23888,25 @@
         <v>70.82057897745131</v>
       </c>
       <c r="M19" t="n">
-        <v>123.1362720599486</v>
+        <v>163.8967753369761</v>
       </c>
       <c r="N19" t="n">
         <v>216.2985998618488</v>
       </c>
       <c r="O19" t="n">
-        <v>291.3521214560641</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>405.314266425598</v>
+        <v>155.8700310189888</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>425.3045869975445</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>74.73126658810133</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>201.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -23943,13 +23943,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>124.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>124.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>122.6518446488253</v>
       </c>
       <c r="H20" t="n">
         <v>116.6876737789043</v>
@@ -23985,25 +23985,25 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>189.6559567470465</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>87.22718592425909</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>369.1328543375554</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>281.4441044690934</v>
       </c>
       <c r="X20" t="n">
-        <v>312.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>231.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -24098,7 +24098,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>5.53621805555548</v>
       </c>
       <c r="E22" t="n">
         <v>0.9809048369565403</v>
@@ -24122,10 +24122,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>69.82057897745131</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>162.8967753369761</v>
       </c>
       <c r="N22" t="n">
         <v>215.2985998618488</v>
@@ -24134,16 +24134,16 @@
         <v>290.3521214560641</v>
       </c>
       <c r="P22" t="n">
-        <v>170.2069013704713</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>275.0612965604691</v>
       </c>
       <c r="R22" t="n">
-        <v>424.3045869975445</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>73.73126658810133</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>7.465352849462363</v>
       </c>
     </row>
     <row r="23">
@@ -24177,10 +24177,10 @@
         <v>169.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>130.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>124.3632896068686</v>
       </c>
       <c r="F23" t="n">
         <v>124.8896287080119</v>
@@ -24234,13 +24234,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>358.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>94.77644291468434</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>198.4474735489134</v>
       </c>
     </row>
     <row r="24">
@@ -24365,19 +24365,19 @@
         <v>162.8967753369761</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>215.2985998618488</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>290.3521214560641</v>
       </c>
       <c r="P25" t="n">
-        <v>347.4708481479496</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>404.314266425598</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>28.92690330483441</v>
+        <v>275.0612965604691</v>
       </c>
       <c r="S25" t="n">
         <v>73.73126658810133</v>
@@ -24414,7 +24414,7 @@
         <v>306.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>108.3391557398494</v>
+        <v>267.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>261.3632896068686</v>
@@ -24426,7 +24426,7 @@
         <v>259.6518446488253</v>
       </c>
       <c r="H26" t="n">
-        <v>253.6876737789043</v>
+        <v>94.68767377889964</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,25 +24459,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>167.6559567470454</v>
+        <v>326.6559567470465</v>
       </c>
       <c r="T26" t="n">
-        <v>438.8361344923829</v>
+        <v>438.836134492383</v>
       </c>
       <c r="U26" t="n">
         <v>506.1328543375554</v>
       </c>
       <c r="V26" t="n">
-        <v>486.8510241668239</v>
+        <v>385.2373224926163</v>
       </c>
       <c r="W26" t="n">
-        <v>336.3734759809473</v>
+        <v>336.3734759809446</v>
       </c>
       <c r="X26" t="n">
-        <v>449.2818334606677</v>
+        <v>290.2818334606648</v>
       </c>
       <c r="Y26" t="n">
-        <v>266.70373100859</v>
+        <v>368.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24490,10 +24490,10 @@
         <v>241.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>59.09991244551918</v>
+        <v>218.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>45.93768689770229</v>
+        <v>204.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>199.6720972219126</v>
@@ -24502,13 +24502,13 @@
         <v>196.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>182.1480264410651</v>
+        <v>23.14802644106044</v>
       </c>
       <c r="H27" t="n">
-        <v>183.4553513373645</v>
+        <v>24.45535133735962</v>
       </c>
       <c r="I27" t="n">
-        <v>53.76081985361269</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24541,19 +24541,19 @@
         <v>312.5769716627245</v>
       </c>
       <c r="T27" t="n">
-        <v>100.9735671043049</v>
+        <v>259.9735671043063</v>
       </c>
       <c r="U27" t="n">
         <v>257.1714446658471</v>
       </c>
       <c r="V27" t="n">
-        <v>131.463467191522</v>
+        <v>112.5106671915168</v>
       </c>
       <c r="W27" t="n">
         <v>289.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>276.8627394453875</v>
+        <v>190.5763592990132</v>
       </c>
       <c r="Y27" t="n">
         <v>256.3913927661343</v>
@@ -24584,7 +24584,7 @@
         <v>101.5479712021858</v>
       </c>
       <c r="H28" t="n">
-        <v>81.36210970817601</v>
+        <v>81.36210970817599</v>
       </c>
       <c r="I28" t="n">
         <v>18.72034086601991</v>
@@ -24599,7 +24599,7 @@
         <v>206.8205789774513</v>
       </c>
       <c r="M28" t="n">
-        <v>159.9470250828526</v>
+        <v>299.8967753369761</v>
       </c>
       <c r="N28" t="n">
         <v>352.2985998618488</v>
@@ -24617,16 +24617,16 @@
         <v>561.3045869975446</v>
       </c>
       <c r="S28" t="n">
-        <v>210.7312665881013</v>
+        <v>199.7888826915654</v>
       </c>
       <c r="T28" t="n">
-        <v>64.90571404724133</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>7.931342094130059</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>56.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>83.37280983870968</v>
@@ -24651,7 +24651,7 @@
         <v>267.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>69.33915573984916</v>
+        <v>228.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>222.3632896068686</v>
@@ -24699,22 +24699,22 @@
         <v>287.6559567470465</v>
       </c>
       <c r="T29" t="n">
-        <v>240.8361344923816</v>
+        <v>240.8361344923748</v>
       </c>
       <c r="U29" t="n">
         <v>467.1328543375554</v>
       </c>
       <c r="V29" t="n">
-        <v>447.8510241668239</v>
+        <v>288.8510241668168</v>
       </c>
       <c r="W29" t="n">
-        <v>456.3734759809475</v>
+        <v>316.3262759809695</v>
       </c>
       <c r="X29" t="n">
-        <v>270.2346334606704</v>
+        <v>251.2818334606611</v>
       </c>
       <c r="Y29" t="n">
-        <v>170.3174326828058</v>
+        <v>329.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -24742,10 +24742,10 @@
         <v>143.1480264410651</v>
       </c>
       <c r="H30" t="n">
-        <v>4.408151337366974</v>
+        <v>144.4553513373645</v>
       </c>
       <c r="I30" t="n">
-        <v>14.76081985361269</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24772,25 +24772,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>328.5483255942661</v>
+        <v>169.5483255942575</v>
       </c>
       <c r="S30" t="n">
-        <v>273.5769716627245</v>
+        <v>114.5769716627163</v>
       </c>
       <c r="T30" t="n">
-        <v>61.97356710430472</v>
+        <v>61.9735671042983</v>
       </c>
       <c r="U30" t="n">
-        <v>218.1714446658471</v>
+        <v>92.8850645194846</v>
       </c>
       <c r="V30" t="n">
-        <v>73.5106671915197</v>
+        <v>232.5106671915202</v>
       </c>
       <c r="W30" t="n">
         <v>250.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>78.86273944538709</v>
+        <v>237.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>217.3913927661343</v>
@@ -24803,7 +24803,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>34.67358412238022</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>90.72524664804467</v>
@@ -24818,10 +24818,10 @@
         <v>92.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>62.54797120218578</v>
+        <v>62.54797120218577</v>
       </c>
       <c r="H31" t="n">
-        <v>42.36210970817601</v>
+        <v>42.36210970817599</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24863,16 +24863,16 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>17.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>65.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>105.4653528494624</v>
+        <v>91.86560175795121</v>
       </c>
     </row>
     <row r="32">
@@ -24882,16 +24882,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>299.9993129555745</v>
+        <v>159.9521129555946</v>
       </c>
       <c r="C32" t="n">
-        <v>267.4745782429939</v>
+        <v>108.4745782429879</v>
       </c>
       <c r="D32" t="n">
-        <v>228.3391557398498</v>
+        <v>69.33915573984376</v>
       </c>
       <c r="E32" t="n">
-        <v>63.36328960686785</v>
+        <v>222.3632896068686</v>
       </c>
       <c r="F32" t="n">
         <v>222.8896287080119</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>128.6559567470447</v>
+        <v>128.6559567470385</v>
       </c>
       <c r="T32" t="n">
         <v>399.836134492383</v>
@@ -24948,10 +24948,10 @@
         <v>456.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>270.2346334606711</v>
+        <v>410.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>170.3174326828056</v>
+        <v>329.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -24964,10 +24964,10 @@
         <v>202.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>39.05271244552279</v>
+        <v>179.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>6.937686897701838</v>
+        <v>165.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>160.6720972219126</v>
@@ -24982,7 +24982,7 @@
         <v>144.4553513373645</v>
       </c>
       <c r="I33" t="n">
-        <v>14.76081985361268</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25015,19 +25015,19 @@
         <v>273.5769716627245</v>
       </c>
       <c r="T33" t="n">
-        <v>61.97356710430449</v>
+        <v>61.97356710429818</v>
       </c>
       <c r="U33" t="n">
-        <v>218.1714446658471</v>
+        <v>59.17144466583966</v>
       </c>
       <c r="V33" t="n">
-        <v>232.5106671915202</v>
+        <v>73.51066719151413</v>
       </c>
       <c r="W33" t="n">
         <v>250.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>78.86273944538664</v>
+        <v>112.5763592990218</v>
       </c>
       <c r="Y33" t="n">
         <v>217.3913927661343</v>
@@ -25040,7 +25040,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>105.1138003370787</v>
       </c>
       <c r="C34" t="n">
         <v>90.72524664804467</v>
@@ -25049,7 +25049,7 @@
         <v>103.5362180555555</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>98.98090483695654</v>
       </c>
       <c r="F34" t="n">
         <v>92.38285596774193</v>
@@ -25058,7 +25058,7 @@
         <v>62.54797120218577</v>
       </c>
       <c r="H34" t="n">
-        <v>42.36210970817599</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25076,7 +25076,7 @@
         <v>260.8967753369761</v>
       </c>
       <c r="N34" t="n">
-        <v>311.230919505127</v>
+        <v>313.2985998618488</v>
       </c>
       <c r="O34" t="n">
         <v>388.3521214560641</v>
@@ -25085,7 +25085,7 @@
         <v>445.4708481479496</v>
       </c>
       <c r="Q34" t="n">
-        <v>502.314266425598</v>
+        <v>425.9628247051842</v>
       </c>
       <c r="R34" t="n">
         <v>522.3045869975446</v>
@@ -25094,16 +25094,16 @@
         <v>171.7312665881013</v>
       </c>
       <c r="T34" t="n">
-        <v>25.90571404724132</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>17.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>44.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>65.44364543010755</v>
@@ -25125,7 +25125,7 @@
         <v>267.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>69.33915573984882</v>
+        <v>228.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>222.3632896068686</v>
@@ -25137,7 +25137,7 @@
         <v>220.6518446488253</v>
       </c>
       <c r="H35" t="n">
-        <v>55.68767377890248</v>
+        <v>74.64047377892359</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25176,13 +25176,13 @@
         <v>399.8361344923829</v>
       </c>
       <c r="U35" t="n">
-        <v>327.085654337559</v>
+        <v>308.1328543375483</v>
       </c>
       <c r="V35" t="n">
-        <v>288.851024166823</v>
+        <v>288.8510241668179</v>
       </c>
       <c r="W35" t="n">
-        <v>456.3734759809475</v>
+        <v>297.3734759809414</v>
       </c>
       <c r="X35" t="n">
         <v>410.2818334606677</v>
@@ -25201,25 +25201,25 @@
         <v>202.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>23.20073888658729</v>
+        <v>179.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>165.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>1.672097221911599</v>
+        <v>160.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>157.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>144.4553513373645</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>14.76081985361269</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25252,7 +25252,7 @@
         <v>273.5769716627245</v>
       </c>
       <c r="T36" t="n">
-        <v>61.97356710430438</v>
+        <v>220.9735671043063</v>
       </c>
       <c r="U36" t="n">
         <v>218.1714446658471</v>
@@ -25264,7 +25264,7 @@
         <v>250.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>237.8627394453875</v>
+        <v>80.81597941530674</v>
       </c>
       <c r="Y36" t="n">
         <v>217.3913927661343</v>
@@ -25295,7 +25295,7 @@
         <v>62.54797120218578</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>42.36210970817601</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -25322,22 +25322,22 @@
         <v>445.4708481479496</v>
       </c>
       <c r="Q37" t="n">
-        <v>502.314266425598</v>
+        <v>498.2279051582986</v>
       </c>
       <c r="R37" t="n">
-        <v>517.5043111749635</v>
+        <v>363.3045869975446</v>
       </c>
       <c r="S37" t="n">
-        <v>12.73126658810133</v>
+        <v>171.7312665881013</v>
       </c>
       <c r="T37" t="n">
-        <v>25.90571404724133</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>17.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>44.37280983870968</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>140.9993129555735</v>
+        <v>299.9993129555745</v>
       </c>
       <c r="C38" t="n">
         <v>267.4745782429939</v>
@@ -25368,10 +25368,10 @@
         <v>222.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>222.8896287080119</v>
+        <v>82.84242870802916</v>
       </c>
       <c r="G38" t="n">
-        <v>80.60464464882801</v>
+        <v>220.6518446488253</v>
       </c>
       <c r="H38" t="n">
         <v>214.6876737789043</v>
@@ -25410,22 +25410,22 @@
         <v>287.6559567470465</v>
       </c>
       <c r="T38" t="n">
-        <v>399.836134492383</v>
+        <v>399.8361344923829</v>
       </c>
       <c r="U38" t="n">
-        <v>467.1328543375554</v>
+        <v>308.1328543375485</v>
       </c>
       <c r="V38" t="n">
-        <v>447.8510241668239</v>
+        <v>288.8510241668186</v>
       </c>
       <c r="W38" t="n">
-        <v>297.3734759809468</v>
+        <v>297.3734759809425</v>
       </c>
       <c r="X38" t="n">
         <v>410.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>170.3174326828055</v>
+        <v>329.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -25435,28 +25435,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>46.65738308739341</v>
+        <v>202.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>179.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>6.937686897701724</v>
+        <v>165.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>160.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>157.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>143.1480264410651</v>
       </c>
       <c r="H39" t="n">
         <v>144.4553513373645</v>
       </c>
       <c r="I39" t="n">
-        <v>14.76081985361268</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25489,22 +25489,22 @@
         <v>273.5769716627245</v>
       </c>
       <c r="T39" t="n">
-        <v>220.9735671043063</v>
+        <v>61.97356710429989</v>
       </c>
       <c r="U39" t="n">
         <v>218.1714446658471</v>
       </c>
       <c r="V39" t="n">
-        <v>232.5106671915202</v>
+        <v>105.8605293830217</v>
       </c>
       <c r="W39" t="n">
         <v>250.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>237.8627394453875</v>
+        <v>78.86273944538203</v>
       </c>
       <c r="Y39" t="n">
-        <v>58.39139276613355</v>
+        <v>217.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -25517,7 +25517,7 @@
         <v>105.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>90.72524664804467</v>
       </c>
       <c r="D40" t="n">
         <v>103.5362180555555</v>
@@ -25529,7 +25529,7 @@
         <v>92.38285596774193</v>
       </c>
       <c r="G40" t="n">
-        <v>62.54797120218577</v>
+        <v>62.54797120218578</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -25556,10 +25556,10 @@
         <v>388.3521214560641</v>
       </c>
       <c r="P40" t="n">
-        <v>445.4708481479496</v>
+        <v>369.1194064275358</v>
       </c>
       <c r="Q40" t="n">
-        <v>455.144951298303</v>
+        <v>502.314266425598</v>
       </c>
       <c r="R40" t="n">
         <v>522.3045869975446</v>
@@ -25574,10 +25574,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>17.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>44.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>65.44364543010755</v>
@@ -25599,19 +25599,19 @@
         <v>347.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>308.3391557398498</v>
+        <v>149.3391557398494</v>
       </c>
       <c r="E41" t="n">
         <v>302.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>168.3027341193482</v>
+        <v>143.8896287080115</v>
       </c>
       <c r="G41" t="n">
-        <v>300.6518446488253</v>
+        <v>141.6518446488249</v>
       </c>
       <c r="H41" t="n">
-        <v>294.6876737789043</v>
+        <v>239.5342775160151</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,22 +25641,22 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>79.4334983257819</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>208.6559567470434</v>
+        <v>367.6559567470465</v>
       </c>
       <c r="T41" t="n">
-        <v>479.836134492383</v>
+        <v>479.8361344923829</v>
       </c>
       <c r="U41" t="n">
-        <v>388.132854337552</v>
+        <v>547.1328543375554</v>
       </c>
       <c r="V41" t="n">
         <v>527.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>377.3734759809456</v>
+        <v>536.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>490.2818334606677</v>
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>282.5565566463266</v>
+        <v>142.5093566463267</v>
       </c>
       <c r="C42" t="n">
         <v>259.0999124455193</v>
@@ -25681,16 +25681,16 @@
         <v>245.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>81.67209722191046</v>
+        <v>240.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>97.58904233788374</v>
+        <v>237.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>223.1480264410651</v>
+        <v>64.14802644106507</v>
       </c>
       <c r="H42" t="n">
-        <v>65.45535133736178</v>
+        <v>65.45535133736453</v>
       </c>
       <c r="I42" t="n">
         <v>94.76081985361269</v>
@@ -25723,7 +25723,7 @@
         <v>408.5483255942661</v>
       </c>
       <c r="S42" t="n">
-        <v>353.5769716627245</v>
+        <v>194.5769716627245</v>
       </c>
       <c r="T42" t="n">
         <v>300.9735671043063</v>
@@ -25741,7 +25741,7 @@
         <v>317.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>138.3913927661324</v>
+        <v>297.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -25805,10 +25805,10 @@
         <v>251.7312665881013</v>
       </c>
       <c r="T43" t="n">
-        <v>55.07140588724786</v>
+        <v>6.140063793117818</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>48.93134209413006</v>
       </c>
       <c r="V43" t="n">
         <v>97.17031021621619</v>
@@ -25842,7 +25842,7 @@
         <v>384.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>384.8896287080119</v>
+        <v>332.3027341193409</v>
       </c>
       <c r="G44" t="n">
         <v>382.6518446488253</v>
@@ -25851,7 +25851,7 @@
         <v>376.6876737789043</v>
       </c>
       <c r="I44" t="n">
-        <v>87.46030541132782</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25878,25 +25878,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.433498325781557</v>
+        <v>2.4334983257815</v>
       </c>
       <c r="S44" t="n">
         <v>449.6559567470465</v>
       </c>
       <c r="T44" t="n">
-        <v>561.8361344923829</v>
+        <v>402.8361344923826</v>
       </c>
       <c r="U44" t="n">
         <v>629.1328543375554</v>
       </c>
       <c r="V44" t="n">
-        <v>450.8510241668214</v>
+        <v>450.8510241668235</v>
       </c>
       <c r="W44" t="n">
-        <v>459.3734759809452</v>
+        <v>618.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>432.2346334606729</v>
+        <v>572.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>491.3174326828064</v>
@@ -25912,13 +25912,13 @@
         <v>364.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>341.0999124455193</v>
+        <v>182.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>327.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>163.6720972219101</v>
+        <v>322.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>319.6362423378769</v>
@@ -25927,7 +25927,7 @@
         <v>305.1480264410651</v>
       </c>
       <c r="H45" t="n">
-        <v>147.4553513373613</v>
+        <v>147.4553513373645</v>
       </c>
       <c r="I45" t="n">
         <v>176.7608198536127</v>
@@ -25954,13 +25954,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>77.57360471312109</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>490.5483255942661</v>
+        <v>331.5483255942661</v>
       </c>
       <c r="S45" t="n">
-        <v>435.5769716627245</v>
+        <v>373.1033763758457</v>
       </c>
       <c r="T45" t="n">
         <v>382.9735671043063</v>
@@ -25969,7 +25969,7 @@
         <v>380.1714446658471</v>
       </c>
       <c r="V45" t="n">
-        <v>254.4634671915283</v>
+        <v>394.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>412.3731429098285</v>
@@ -25978,7 +25978,7 @@
         <v>399.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>220.391392766132</v>
+        <v>379.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -26048,10 +26048,10 @@
         <v>130.9313420941301</v>
       </c>
       <c r="V46" t="n">
-        <v>179.1703102162162</v>
+        <v>159.7728599620927</v>
       </c>
       <c r="W46" t="n">
-        <v>186.9753595845862</v>
+        <v>206.3728098387097</v>
       </c>
       <c r="X46" t="n">
         <v>227.4436454301076</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>980688.7752757032</v>
+        <v>980688.7752757031</v>
       </c>
     </row>
     <row r="3">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2453637.364912872</v>
+        <v>2453637.364912873</v>
       </c>
     </row>
     <row r="5">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4477409.547958199</v>
+        <v>4477409.547958198</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5191759.462734212</v>
+        <v>5191759.46273421</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5905572.581790606</v>
+        <v>5905572.581790602</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6170369.197246855</v>
+        <v>6170369.197246852</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6676639.750021382</v>
+        <v>6676639.750021379</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7152728.772714339</v>
+        <v>7152728.772714338</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7628817.795407297</v>
+        <v>7628817.795407294</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8104906.818100254</v>
+        <v>8104906.818100251</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8439814.845453573</v>
+        <v>8439814.845453572</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8677445.274940303</v>
+        <v>8677445.274940304</v>
       </c>
     </row>
   </sheetData>
@@ -26269,22 +26269,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1325653.730673453</v>
+        <v>1325653.730673452</v>
       </c>
       <c r="C2" t="n">
-        <v>1325653.730673453</v>
+        <v>1325653.730673452</v>
       </c>
       <c r="D2" t="n">
-        <v>1325653.730673453</v>
+        <v>1325653.730673452</v>
       </c>
       <c r="E2" t="n">
-        <v>1134624.579059051</v>
+        <v>1134624.57905905</v>
       </c>
       <c r="F2" t="n">
         <v>1246944.001117978</v>
       </c>
       <c r="G2" t="n">
-        <v>1282968.361901513</v>
+        <v>1282968.361901514</v>
       </c>
       <c r="H2" t="n">
         <v>1284863.614301514</v>
@@ -26296,22 +26296,22 @@
         <v>750239.0844798678</v>
       </c>
       <c r="K2" t="n">
-        <v>856960.2408473346</v>
+        <v>856960.2408473347</v>
       </c>
       <c r="L2" t="n">
-        <v>856960.2408473347</v>
+        <v>856960.2408473348</v>
       </c>
       <c r="M2" t="n">
         <v>856960.2408473347</v>
       </c>
       <c r="N2" t="n">
-        <v>856960.2408473347</v>
+        <v>856960.2408473348</v>
       </c>
       <c r="O2" t="n">
-        <v>636839.6934302835</v>
+        <v>636839.6934302833</v>
       </c>
       <c r="P2" t="n">
-        <v>399975.4910854676</v>
+        <v>399975.4910854675</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>650157.190467549</v>
+        <v>654271.7892353594</v>
       </c>
       <c r="C4" t="n">
-        <v>648525.8737379931</v>
+        <v>652640.4725058037</v>
       </c>
       <c r="D4" t="n">
-        <v>646892.344025474</v>
+        <v>651006.9427932845</v>
       </c>
       <c r="E4" t="n">
-        <v>533638.8289275995</v>
+        <v>536838.8786083721</v>
       </c>
       <c r="F4" t="n">
-        <v>597919.4012685325</v>
+        <v>601658.6065685716</v>
       </c>
       <c r="G4" t="n">
-        <v>617250.8104125027</v>
+        <v>621161.853521034</v>
       </c>
       <c r="H4" t="n">
-        <v>616757.0970272053</v>
+        <v>620677.1842309204</v>
       </c>
       <c r="I4" t="n">
-        <v>615162.4170818209</v>
+        <v>619082.504285536</v>
       </c>
       <c r="J4" t="n">
-        <v>302661.6105060843</v>
+        <v>304020.7076947953</v>
       </c>
       <c r="K4" t="n">
-        <v>363334.8066716149</v>
+        <v>365202.4113257793</v>
       </c>
       <c r="L4" t="n">
-        <v>362269.1111222028</v>
+        <v>364136.7157763673</v>
       </c>
       <c r="M4" t="n">
-        <v>361201.892405058</v>
+        <v>363069.4970592224</v>
       </c>
       <c r="N4" t="n">
-        <v>360133.1392048605</v>
+        <v>362000.7438590251</v>
       </c>
       <c r="O4" t="n">
-        <v>246839.873627791</v>
+        <v>248389.183533651</v>
       </c>
       <c r="P4" t="n">
-        <v>137282.0352189254</v>
+        <v>139091.176626769</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>158872.1402059036</v>
+        <v>154757.5414380923</v>
       </c>
       <c r="C6" t="n">
-        <v>606740.4569354597</v>
+        <v>602625.8581676482</v>
       </c>
       <c r="D6" t="n">
-        <v>608373.9866479785</v>
+        <v>604259.3878801678</v>
       </c>
       <c r="E6" t="n">
-        <v>372382.9771314512</v>
+        <v>369182.9274506784</v>
       </c>
       <c r="F6" t="n">
-        <v>556006.8598494458</v>
+        <v>552267.6545494068</v>
       </c>
       <c r="G6" t="n">
-        <v>590302.5004890106</v>
+        <v>586391.4573804796</v>
       </c>
       <c r="H6" t="n">
-        <v>607007.3972743086</v>
+        <v>603087.3100705935</v>
       </c>
       <c r="I6" t="n">
-        <v>609402.077219693</v>
+        <v>605481.9900159783</v>
       </c>
       <c r="J6" t="n">
-        <v>299925.4069737836</v>
+        <v>298566.3097850725</v>
       </c>
       <c r="K6" t="n">
-        <v>397062.6761757197</v>
+        <v>395195.0715215554</v>
       </c>
       <c r="L6" t="n">
-        <v>448528.3717251319</v>
+        <v>446660.7670709675</v>
       </c>
       <c r="M6" t="n">
-        <v>463995.5904422768</v>
+        <v>462127.9857881123</v>
       </c>
       <c r="N6" t="n">
-        <v>465864.3436424742</v>
+        <v>463996.7389883097</v>
       </c>
       <c r="O6" t="n">
-        <v>365762.5818024925</v>
+        <v>364213.2718966323</v>
       </c>
       <c r="P6" t="n">
-        <v>245349.8758665423</v>
+        <v>243540.7344586985</v>
       </c>
     </row>
   </sheetData>
@@ -26978,7 +26978,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>217</v>
@@ -27439,13 +27439,13 @@
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>58.47118268983581</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>396.6876737789043</v>
       </c>
       <c r="I2" t="n">
-        <v>107.4603054113278</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27496,7 +27496,7 @@
         <v>400</v>
       </c>
       <c r="W2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>146.0661069588086</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27533,7 +27533,7 @@
         <v>326.4553513373645</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>196.7608198536127</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>97.57360471312109</v>
       </c>
       <c r="R3" t="n">
-        <v>4.548325594266075</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27612,7 +27612,7 @@
         <v>224.362109708176</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>161.7203408660199</v>
       </c>
       <c r="J4" t="n">
         <v>0.2087029342684161</v>
@@ -27627,10 +27627,10 @@
         <v>400</v>
       </c>
       <c r="N4" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>400</v>
+        <v>66.96141711880448</v>
       </c>
       <c r="P4" t="n">
         <v>400</v>
@@ -27639,10 +27639,10 @@
         <v>400</v>
       </c>
       <c r="R4" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>353.7312665881013</v>
       </c>
       <c r="T4" t="n">
         <v>207.9057140472413</v>
@@ -27654,7 +27654,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>345.4626264112106</v>
+        <v>396.6876737789043</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27721,10 +27721,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>151.3755255074642</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.1480264410651</v>
@@ -27797,19 +27797,19 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>260.5154474066165</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>109.2925343426962</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27861,22 +27861,22 @@
         <v>349.8205789774513</v>
       </c>
       <c r="M7" t="n">
-        <v>400</v>
+        <v>148.8801722734904</v>
       </c>
       <c r="N7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>353.7312665881013</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27916,10 +27916,10 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>165.2832886163611</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
@@ -27961,7 +27961,7 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>262.4817217703543</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -28001,10 +28001,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.1480264410651</v>
       </c>
       <c r="H9" t="n">
-        <v>51.88215398828783</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>196.7608198536127</v>
@@ -28037,13 +28037,13 @@
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>242.0174837162117</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28052,10 +28052,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28071,10 +28071,10 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
@@ -28092,16 +28092,16 @@
         <v>0.2087029342684161</v>
       </c>
       <c r="K10" t="n">
-        <v>230.9060197027824</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>349.8205789774513</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>400</v>
+        <v>210.5876757906757</v>
       </c>
       <c r="N10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>400</v>
@@ -28110,10 +28110,10 @@
         <v>400</v>
       </c>
       <c r="Q10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>353.7312665881013</v>
@@ -28171,7 +28171,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -28183,13 +28183,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>25.89810193322131</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>217</v>
@@ -28250,11 +28250,11 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>215.123862632733</v>
+      </c>
+      <c r="L12" t="n">
         <v>217</v>
       </c>
-      <c r="L12" t="n">
-        <v>81.18801524954677</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -28262,7 +28262,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>217</v>
+        <v>131.6841741706915</v>
       </c>
       <c r="P12" t="n">
         <v>217</v>
@@ -28408,10 +28408,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10.9014671711443</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>181.4334983257819</v>
+        <v>260</v>
       </c>
       <c r="S14" t="n">
         <v>260</v>
@@ -28481,13 +28481,13 @@
         <v>260</v>
       </c>
       <c r="I15" t="n">
-        <v>260</v>
+        <v>196.7608198536127</v>
       </c>
       <c r="J15" t="n">
-        <v>159.2417077506938</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>219.3803434724162</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -28496,7 +28496,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>196.9402317796766</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>114.8488000566545</v>
+        <v>97.57360471312109</v>
       </c>
       <c r="R15" t="n">
         <v>260</v>
@@ -28639,7 +28639,7 @@
         <v>279</v>
       </c>
       <c r="I17" t="n">
-        <v>107.4603054113278</v>
+        <v>141.8748510340569</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>215.8480439485114</v>
+        <v>181.4334983257819</v>
       </c>
       <c r="S17" t="n">
         <v>279</v>
@@ -28876,7 +28876,7 @@
         <v>280</v>
       </c>
       <c r="I20" t="n">
-        <v>125.2930919170756</v>
+        <v>125.2930919170765</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -29113,7 +29113,7 @@
         <v>280</v>
       </c>
       <c r="I23" t="n">
-        <v>125.293091917076</v>
+        <v>125.2930919170764</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -29374,7 +29374,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>53.43813658879195</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>143</v>
@@ -29432,22 +29432,22 @@
         <v>143</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="L27" t="n">
         <v>143</v>
       </c>
       <c r="M27" t="n">
-        <v>50.3302709362222</v>
+        <v>115.5773386831053</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -29587,7 +29587,7 @@
         <v>182</v>
       </c>
       <c r="I29" t="n">
-        <v>111.4618914346809</v>
+        <v>110.8953897604626</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>181.4334983257819</v>
+        <v>182.000000000001</v>
       </c>
       <c r="S29" t="n">
         <v>182</v>
@@ -29824,7 +29824,7 @@
         <v>182</v>
       </c>
       <c r="I32" t="n">
-        <v>111.4618914346811</v>
+        <v>107.4603054113278</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>97.57360471312109</v>
+        <v>105.0860162097935</v>
       </c>
       <c r="R33" t="n">
         <v>182</v>
@@ -30061,7 +30061,7 @@
         <v>182</v>
       </c>
       <c r="I35" t="n">
-        <v>107.4603054113278</v>
+        <v>110.8953897604622</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>181.4334983257819</v>
+        <v>182.0000000000006</v>
       </c>
       <c r="S35" t="n">
         <v>182</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>105.0860162097938</v>
+        <v>97.57360471312109</v>
       </c>
       <c r="R36" t="n">
         <v>182</v>
@@ -30298,7 +30298,7 @@
         <v>182</v>
       </c>
       <c r="I38" t="n">
-        <v>111.4618914346817</v>
+        <v>111.4618914346808</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30550,7 +30550,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>54.60307234438226</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -30559,7 +30559,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>53.43813658879195</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>102</v>
@@ -30617,28 +30617,28 @@
         <v>102</v>
       </c>
       <c r="J42" t="n">
-        <v>46.37146587879195</v>
+        <v>102</v>
       </c>
       <c r="K42" t="n">
-        <v>9.260584335429741</v>
+        <v>102</v>
       </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>102</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>102</v>
       </c>
       <c r="O42" t="n">
+        <v>50.0377358490566</v>
+      </c>
+      <c r="P42" t="n">
         <v>102</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
       <c r="Q42" t="n">
-        <v>97.57360471312109</v>
+        <v>102</v>
       </c>
       <c r="R42" t="n">
         <v>102</v>
@@ -30787,7 +30787,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>17.18592964824121</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -30796,7 +30796,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>20</v>
@@ -30857,22 +30857,22 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L45" t="n">
         <v>20</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N45" t="n">
+        <v>9.811320754716981</v>
+      </c>
+      <c r="O45" t="n">
         <v>20</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q45" t="n">
         <v>20</v>
@@ -33014,7 +33014,7 @@
         <v>186.2689698492462</v>
       </c>
       <c r="P26" t="n">
-        <v>158.9762562814072</v>
+        <v>158.9762562814071</v>
       </c>
       <c r="Q26" t="n">
         <v>119.3845477386935</v>
@@ -33251,7 +33251,7 @@
         <v>186.2689698492462</v>
       </c>
       <c r="P29" t="n">
-        <v>158.9762562814072</v>
+        <v>158.9762562814071</v>
       </c>
       <c r="Q29" t="n">
         <v>119.3845477386935</v>
@@ -33488,7 +33488,7 @@
         <v>186.2689698492462</v>
       </c>
       <c r="P32" t="n">
-        <v>158.9762562814072</v>
+        <v>158.9762562814071</v>
       </c>
       <c r="Q32" t="n">
         <v>119.3845477386935</v>
@@ -33725,7 +33725,7 @@
         <v>186.2689698492462</v>
       </c>
       <c r="P35" t="n">
-        <v>158.9762562814072</v>
+        <v>158.9762562814071</v>
       </c>
       <c r="Q35" t="n">
         <v>119.3845477386935</v>
@@ -33962,7 +33962,7 @@
         <v>186.2689698492462</v>
       </c>
       <c r="P38" t="n">
-        <v>158.9762562814072</v>
+        <v>158.976256281407</v>
       </c>
       <c r="Q38" t="n">
         <v>119.3845477386935</v>
@@ -34199,7 +34199,7 @@
         <v>186.2689698492462</v>
       </c>
       <c r="P41" t="n">
-        <v>158.9762562814072</v>
+        <v>158.9762562814071</v>
       </c>
       <c r="Q41" t="n">
         <v>119.3845477386935</v>
@@ -34436,7 +34436,7 @@
         <v>186.2689698492462</v>
       </c>
       <c r="P44" t="n">
-        <v>158.976256281407</v>
+        <v>158.9762562814071</v>
       </c>
       <c r="Q44" t="n">
         <v>119.3845477386935</v>
@@ -34746,13 +34746,13 @@
         <v>58.78727013681922</v>
       </c>
       <c r="K2" t="n">
-        <v>506</v>
+        <v>140.6272613065327</v>
       </c>
       <c r="L2" t="n">
         <v>174.4605527638191</v>
       </c>
       <c r="M2" t="n">
-        <v>483.5974361390377</v>
+        <v>342.9701748325049</v>
       </c>
       <c r="N2" t="n">
         <v>506</v>
@@ -34764,7 +34764,7 @@
         <v>158.6891962407256</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34986,22 +34986,22 @@
         <v>140.6272613065327</v>
       </c>
       <c r="L5" t="n">
+        <v>174.4605527638191</v>
+      </c>
+      <c r="M5" t="n">
         <v>506</v>
       </c>
-      <c r="M5" t="n">
-        <v>286.1410241122036</v>
-      </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="O5" t="n">
-        <v>506</v>
+        <v>116.0211002751538</v>
       </c>
       <c r="P5" t="n">
-        <v>506</v>
+        <v>158.6891962407256</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>342.9701748325049</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35062,10 +35062,10 @@
         <v>181.0932760489965</v>
       </c>
       <c r="K6" t="n">
-        <v>286.6196565275837</v>
+        <v>285.8342571654267</v>
       </c>
       <c r="L6" t="n">
-        <v>401.738759005398</v>
+        <v>402.5241583675549</v>
       </c>
       <c r="M6" t="n">
         <v>236.8250421645043</v>
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>58.78727013681922</v>
+        <v>489.092006722976</v>
       </c>
       <c r="K8" t="n">
         <v>140.6272613065327</v>
       </c>
       <c r="L8" t="n">
-        <v>286.1410241122036</v>
+        <v>174.4605527638191</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>418.6654382463483</v>
       </c>
       <c r="O8" t="n">
-        <v>506</v>
+        <v>116.0211002751538</v>
       </c>
       <c r="P8" t="n">
-        <v>506</v>
+        <v>158.6891962407256</v>
       </c>
       <c r="Q8" t="n">
         <v>506</v>
@@ -35299,7 +35299,7 @@
         <v>181.0932760489965</v>
       </c>
       <c r="K9" t="n">
-        <v>286.6196565275837</v>
+        <v>285.8342571654267</v>
       </c>
       <c r="L9" t="n">
         <v>402.5241583675549</v>
@@ -35311,7 +35311,7 @@
         <v>288.4682953916737</v>
       </c>
       <c r="O9" t="n">
-        <v>381.4067640500234</v>
+        <v>382.1921634121803</v>
       </c>
       <c r="P9" t="n">
         <v>226.6183630052193</v>
@@ -35451,13 +35451,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>109.5396945886722</v>
       </c>
       <c r="J11" t="n">
         <v>489.092006722976</v>
       </c>
       <c r="K11" t="n">
-        <v>342.2926995528811</v>
+        <v>357.6272613065327</v>
       </c>
       <c r="L11" t="n">
         <v>174.4605527638191</v>
@@ -35466,10 +35466,10 @@
         <v>506</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>56.559241983458</v>
       </c>
       <c r="O11" t="n">
-        <v>333.0211002751538</v>
+        <v>116.0211002751538</v>
       </c>
       <c r="P11" t="n">
         <v>158.6891962407256</v>
@@ -35478,7 +35478,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>35.5665016742181</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -35530,16 +35530,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.511598253858246</v>
+        <v>20.23918014638732</v>
       </c>
       <c r="J12" t="n">
         <v>181.0932760489965</v>
       </c>
       <c r="K12" t="n">
-        <v>503.6196565275837</v>
+        <v>501.7435191603167</v>
       </c>
       <c r="L12" t="n">
-        <v>483.7121736171017</v>
+        <v>231.4348219077568</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -35551,10 +35551,10 @@
         <v>506</v>
       </c>
       <c r="P12" t="n">
-        <v>224.4676511646698</v>
+        <v>443.6183630052193</v>
       </c>
       <c r="Q12" t="n">
-        <v>102.1511999433455</v>
+        <v>119.4263952868789</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35691,31 +35691,31 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>58.78727013681922</v>
+        <v>489.092006722976</v>
       </c>
       <c r="K14" t="n">
-        <v>268.0790891780107</v>
+        <v>400.6272613065327</v>
       </c>
       <c r="L14" t="n">
+        <v>185.3620199349634</v>
+      </c>
+      <c r="M14" t="n">
         <v>506</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>506</v>
+        <v>116.0211002751538</v>
       </c>
       <c r="P14" t="n">
         <v>158.6891962407256</v>
       </c>
       <c r="Q14" t="n">
-        <v>506</v>
+        <v>69.19746940098577</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>78.5665016742181</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -35767,25 +35767,25 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>45.51159825385825</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>340.3349837996903</v>
+        <v>181.0932760489965</v>
       </c>
       <c r="K15" t="n">
-        <v>506</v>
+        <v>286.6196565275837</v>
       </c>
       <c r="L15" t="n">
         <v>402.5241583675549</v>
       </c>
       <c r="M15" t="n">
-        <v>99.58796555388798</v>
+        <v>236.8250421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>288.4682953916737</v>
       </c>
       <c r="O15" t="n">
-        <v>382.1921634121803</v>
+        <v>380.6204408868587</v>
       </c>
       <c r="P15" t="n">
         <v>226.6183630052193</v>
@@ -35928,31 +35928,31 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>489.092006722976</v>
+        <v>58.78727013681922</v>
       </c>
       <c r="K17" t="n">
-        <v>506.0000000000001</v>
+        <v>140.6272613065327</v>
       </c>
       <c r="L17" t="n">
+        <v>174.4605527638191</v>
+      </c>
+      <c r="M17" t="n">
         <v>506</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="O17" t="n">
         <v>116.0211002751538</v>
       </c>
       <c r="P17" t="n">
-        <v>352.0279029346962</v>
+        <v>158.6891962407256</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>342.9701748325049</v>
       </c>
       <c r="R17" t="n">
-        <v>34.41454562272955</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -36013,7 +36013,7 @@
         <v>286.6196565275837</v>
       </c>
       <c r="L18" t="n">
-        <v>110.1657814192149</v>
+        <v>402.5241583675549</v>
       </c>
       <c r="M18" t="n">
         <v>236.8250421645043</v>
@@ -36022,7 +36022,7 @@
         <v>288.4682953916737</v>
       </c>
       <c r="O18" t="n">
-        <v>382.1921634121803</v>
+        <v>89.8337864638403</v>
       </c>
       <c r="P18" t="n">
         <v>226.6183630052193</v>
@@ -36162,10 +36162,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>17.83278650574782</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>58.78727013681922</v>
+        <v>489.092006722976</v>
       </c>
       <c r="K20" t="n">
         <v>140.6272613065327</v>
@@ -36174,16 +36174,16 @@
         <v>174.4605527638191</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>418.6654382463483</v>
       </c>
       <c r="N20" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>116.0211002751538</v>
       </c>
       <c r="P20" t="n">
-        <v>483.8265845674824</v>
+        <v>158.6891962407256</v>
       </c>
       <c r="Q20" t="n">
         <v>506</v>
@@ -36256,10 +36256,10 @@
         <v>236.8250421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>288.4682953916737</v>
+        <v>199.956069524777</v>
       </c>
       <c r="O21" t="n">
-        <v>293.6799375452835</v>
+        <v>382.1921634121803</v>
       </c>
       <c r="P21" t="n">
         <v>7.467651164669803</v>
@@ -36399,25 +36399,25 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>17.83278650574815</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>58.78727013681922</v>
+        <v>489.092006722976</v>
       </c>
       <c r="K23" t="n">
-        <v>140.6272613065327</v>
+        <v>506.0000000000001</v>
       </c>
       <c r="L23" t="n">
         <v>174.4605527638191</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>53.29269955288092</v>
       </c>
       <c r="N23" t="n">
-        <v>441.1584886019107</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>506</v>
+        <v>116.0211002751538</v>
       </c>
       <c r="P23" t="n">
         <v>158.6891962407256</v>
@@ -36487,19 +36487,19 @@
         <v>286.6196565275837</v>
       </c>
       <c r="L24" t="n">
-        <v>383.3295160517825</v>
+        <v>402.5241583675549</v>
       </c>
       <c r="M24" t="n">
         <v>236.8250421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>288.4682953916737</v>
       </c>
       <c r="O24" t="n">
-        <v>382.1921634121803</v>
+        <v>293.6799375452835</v>
       </c>
       <c r="P24" t="n">
-        <v>226.6183630052193</v>
+        <v>7.467651164669803</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>116.0211002751538</v>
       </c>
       <c r="P26" t="n">
-        <v>158.6891962407258</v>
+        <v>158.6891962407257</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36718,25 +36718,25 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
+        <v>96.62853412120805</v>
+      </c>
+      <c r="K27" t="n">
         <v>159</v>
       </c>
-      <c r="K27" t="n">
-        <v>154.1409356680008</v>
-      </c>
       <c r="L27" t="n">
-        <v>157.4348219077568</v>
+        <v>159</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>48.47957228987985</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="P27" t="n">
-        <v>159</v>
+        <v>7.467651164669803</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36894,7 +36894,7 @@
         <v>116.0211002751538</v>
       </c>
       <c r="P29" t="n">
-        <v>158.6891962407258</v>
+        <v>158.6891962407257</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36955,16 +36955,16 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="K30" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>159</v>
+        <v>14.43482190775684</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>138.1409356680008</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -36973,7 +36973,7 @@
         <v>159</v>
       </c>
       <c r="P30" t="n">
-        <v>152.5757575757576</v>
+        <v>159</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -37067,7 +37067,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>31.06865790586994</v>
+        <v>31.06865790586993</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -37131,7 +37131,7 @@
         <v>116.0211002751538</v>
       </c>
       <c r="P32" t="n">
-        <v>158.6891962407258</v>
+        <v>158.6891962407257</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37195,10 +37195,10 @@
         <v>159</v>
       </c>
       <c r="K33" t="n">
-        <v>138.1409356680008</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>14.43482190775684</v>
+        <v>145.0633460790851</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -37213,7 +37213,7 @@
         <v>159</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>7.512411496672456</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37368,7 +37368,7 @@
         <v>116.0211002751538</v>
       </c>
       <c r="P35" t="n">
-        <v>158.6891962407258</v>
+        <v>158.6891962407257</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37429,28 +37429,28 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>138.1409356680008</v>
       </c>
       <c r="K36" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>14.43482190775684</v>
       </c>
       <c r="M36" t="n">
-        <v>123.1608730066583</v>
+        <v>159</v>
       </c>
       <c r="N36" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>159</v>
       </c>
       <c r="P36" t="n">
-        <v>7.467651164669803</v>
+        <v>159</v>
       </c>
       <c r="Q36" t="n">
-        <v>7.512411496672755</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37605,7 +37605,7 @@
         <v>116.0211002751538</v>
       </c>
       <c r="P38" t="n">
-        <v>158.6891962407258</v>
+        <v>158.6891962407256</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37666,22 +37666,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="K39" t="n">
-        <v>159</v>
+        <v>130.673284503331</v>
       </c>
       <c r="L39" t="n">
         <v>14.43482190775684</v>
       </c>
       <c r="M39" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>159</v>
       </c>
       <c r="O39" t="n">
-        <v>130.673284503331</v>
+        <v>159</v>
       </c>
       <c r="P39" t="n">
         <v>7.467651164669803</v>
@@ -37778,7 +37778,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>31.06865790586993</v>
+        <v>31.06865790586994</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -37842,7 +37842,7 @@
         <v>116.0211002751538</v>
       </c>
       <c r="P41" t="n">
-        <v>158.6891962407258</v>
+        <v>158.6891962407257</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37903,28 +37903,28 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>55.62853412120805</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="L42" t="n">
-        <v>116.4348219077568</v>
+        <v>14.43482190775684</v>
       </c>
       <c r="M42" t="n">
         <v>159</v>
       </c>
       <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>78.08600625991389</v>
+      </c>
+      <c r="P42" t="n">
         <v>159</v>
       </c>
-      <c r="O42" t="n">
-        <v>101.5103646112766</v>
-      </c>
-      <c r="P42" t="n">
-        <v>93.63057105672408</v>
-      </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.426395286878908</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -38079,7 +38079,7 @@
         <v>116.0211002751538</v>
       </c>
       <c r="P44" t="n">
-        <v>158.6891962407256</v>
+        <v>158.6891962407257</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="K45" t="n">
         <v>159</v>
@@ -38149,16 +38149,16 @@
         <v>34.43482190775684</v>
       </c>
       <c r="M45" t="n">
-        <v>118.1409356680008</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="O45" t="n">
-        <v>159</v>
+        <v>90.67328450333096</v>
       </c>
       <c r="P45" t="n">
-        <v>159</v>
+        <v>27.4676511646698</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
